--- a/movies_scraped.xlsx
+++ b/movies_scraped.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lione\Desktop\codes\Cinema_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lione\Desktop\Projets\Cinema_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DE4F11-852A-4A53-958E-16A4194155D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A30FED-403D-403B-BDEB-B0253CA0B60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="11358" windowHeight="12228" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="114">
   <si>
     <t>movie_id</t>
   </si>
@@ -70,253 +70,298 @@
     <t>def_budget</t>
   </si>
   <si>
-    <t>tt15424716</t>
-  </si>
-  <si>
-    <t>En Garde</t>
-  </si>
-  <si>
-    <t>Ci xin qie gu</t>
-  </si>
-  <si>
-    <t>Nelicia Low</t>
-  </si>
-  <si>
-    <t>Hsiu-Fu Liu | Yu-Ning Tsao | Ning Ding | Lin Tsu-heng | Rosen Tsai</t>
-  </si>
-  <si>
-    <t>Drama | Sport | Thriller</t>
-  </si>
-  <si>
-    <t>Singapore | Taiwan | Poland</t>
-  </si>
-  <si>
-    <t>Mandarin</t>
-  </si>
-  <si>
-    <t>Harine Films | Potocol</t>
-  </si>
-  <si>
-    <t>tt33244668</t>
-  </si>
-  <si>
-    <t>Anaconda</t>
-  </si>
-  <si>
-    <t>Tom Gormican</t>
-  </si>
-  <si>
-    <t>Jack Black | Paul Rudd | Steve Zahn | Thandiwe Newton | Daniela Melchior | Selton Mello | Ice Cube | Ione Skye | Rui Ricardo Diaz | John Billingsley | Sebastian Sero | Diego Arnary | Dan Silveira | Anna Francesca Armenia | Jarred Blakiston | John Voce | Lisa Kay | Ron Smyck | Ben Lawson | Renee Herbert | Romeo Ellard | Reagan George | Aimee Bah | Jack Waters | Yasmin Kassim | Gabriel Jose | Cooper Matthews | Jankester Ayala | Cheree Cassidy | Paulo Borges</t>
-  </si>
-  <si>
-    <t>Action | Adventure | Comedy</t>
-  </si>
-  <si>
-    <t>USA</t>
+    <t>tt32642638</t>
+  </si>
+  <si>
+    <t>Rusalka</t>
+  </si>
+  <si>
+    <t>Claudiu Mitcu</t>
+  </si>
+  <si>
+    <t>Pia Bratianu | Aida Economu | Diana Gheorghian | Claudiu Istodor | Rodica Lazar | Silvana Mihai | Maia Morgenstern | Rodica Negrea | Nelu Serghei | Doina Severin</t>
+  </si>
+  <si>
+    <t>Drama</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Romanian | English | Russian</t>
+  </si>
+  <si>
+    <t>tt35487769</t>
+  </si>
+  <si>
+    <t>Alice au pays des merveilles: Dive in Wonderland</t>
+  </si>
+  <si>
+    <t>Fushigi no Kuni de Arisu to Daibu in Wandârando</t>
+  </si>
+  <si>
+    <t>Toshiya Shinohara</t>
+  </si>
+  <si>
+    <t>Nanoka Hara | Maika Pugh | Natsuki Hanae | Subaru Kimura | Ryûichi Kosugi | Shôtarô Mamiya | Mayu Matsuoka | Toshiyuki Morikawa | Ayumu Murase | Yuki Ono | Keiko Toda | Kappei Yamaguchi | Kôji Yamamoto | Takahiro Yamamoto | Norito Yashima</t>
+  </si>
+  <si>
+    <t>Animation | Family | Fantasy</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>P.A. Works | TBS Television</t>
+  </si>
+  <si>
+    <t>tt33035860</t>
+  </si>
+  <si>
+    <t>Les courageux</t>
+  </si>
+  <si>
+    <t>Jasmin Gordon</t>
+  </si>
+  <si>
+    <t>Ophélia Kolb | Jasmine Kalisz Saurer | Paul Besnier | Arthur Devaux | Sabine Timoteo | Roger Bonjour | Claudia Grob | Alexandra Karamisaris | Nabil Rafi | Michel Voïta</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>Maximage</t>
+  </si>
+  <si>
+    <t>tt35932888</t>
+  </si>
+  <si>
+    <t>Forêt rouge</t>
+  </si>
+  <si>
+    <t>Laurie Lassalle</t>
+  </si>
+  <si>
+    <t>Documentary</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>No Info</t>
+  </si>
+  <si>
+    <t>Les Films de l'oeil sauvage | Les Alchimistes | Vià93</t>
+  </si>
+  <si>
+    <t>tt32141377</t>
+  </si>
+  <si>
+    <t>28 ans plus tard: Le temple des morts</t>
+  </si>
+  <si>
+    <t>28 Years Later: The Bone Temple</t>
+  </si>
+  <si>
+    <t>Nia DaCosta</t>
+  </si>
+  <si>
+    <t>Jack O'Connell | Alfie Williams | Connor Newall | Erin Kellyman | Maura Bird | Ghazi Al Ruffai | Robert Rhodes | Emma Laird | Sam Locke | Gareth Locke | Chi Lewis-Parry | Ralph Fiennes | Celi Crossland | Mirren Mack | Gordon Alexander | Louis Ashbourne Serkis | David Sterne | Elliot Benn | Lynne Anne Rodgers | Natalie Cousteau</t>
+  </si>
+  <si>
+    <t>Horror</t>
+  </si>
+  <si>
+    <t>UK | USA</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
-    <t>Columbia Pictures | Fully Formed Entertainment | TSG Entertainment</t>
-  </si>
-  <si>
-    <t>tt33322174</t>
-  </si>
-  <si>
-    <t>Qui brille au combat</t>
-  </si>
-  <si>
-    <t>Joséphine Japy</t>
-  </si>
-  <si>
-    <t>Mélanie Laurent | Pierre-Yves Cardinal | Angelina Woreth | Sarah Pachoud | Félix Kysyl | Juliette Gasquet | Thomas Gioria | Ilinka Lony | Lucas Cenciai | Najim Zeghoudi | Maxence Tual | Claire Tran | Anne Loiret | Birane Ba | Stéphane Varupenne | Serpentine Teyssier | Benjamin Lepennetier | Ludivine Colle | Pascal Decolland | Arnaud Straebler | Louis Torres | Eric Verdin | Jean-Marc Desmond | Alessandro Sanna | Maël Vitolini Naldini | Marnie Hervas | Elsa Vitolini Naldini | Michaël Sisowath | Norhene Lajmi | Tiphaine Gardon</t>
-  </si>
-  <si>
-    <t>Drama</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>French</t>
-  </si>
-  <si>
-    <t>Cowboys Films | France 3 Cinéma | The Man</t>
-  </si>
-  <si>
-    <t>tt30343021</t>
-  </si>
-  <si>
-    <t>Sur un Air de Blues</t>
-  </si>
-  <si>
-    <t>Song Sung Blue</t>
-  </si>
-  <si>
-    <t>Craig Brewer</t>
-  </si>
-  <si>
-    <t>Hugh Jackman | Kate Hudson | Ella Anderson | Hudson Hensley | King Princess | Michael Imperioli | Fisher Stevens | Jim Belushi | Mustafa Shakir | John Beckwith | Jayson Warner Smith | Cecelia Riddett | Sean Allan Krill | Jim Conroy | Kena Anae | Darius Rose | Shyaporn Theerakulstit | Chacha Tahng | Faye Tamasa | Darius de Haas | T. Oliver Reid | Charles E. Wallace | Charles Gray | Carey Van Driest | Eva Kaminsky | Beth Malone | Rachel Cartwright | Leah Curney | Anya Banerjee | Ben Krieger</t>
+    <t>Columbia Pictures | DNA Films | Decibel Films</t>
+  </si>
+  <si>
+    <t>tt35495035</t>
+  </si>
+  <si>
+    <t>L'affaire Bojarski</t>
+  </si>
+  <si>
+    <t>Jean-Paul Salomé</t>
+  </si>
+  <si>
+    <t>Reda Kateb | Sara Giraudeau | Bastien Bouillon | Pierre Lottin | Quentin Dolmaire | Victor Poirier | Olivier Loustau | Cédric Weber | Camille Japy | Francis Leplay | Arthur Teboul | Lolita Chammah | Margaux Rossi | François Perache | Christophe Kourotchkine | Frédéric Buret | Pierre Giraud | Helena Sadowy | Julien Massetti | Alain Bouzigues | Nicolas Delys | Axelle Simon | Mathieu Thouvenot | Yves Heck | Régis Romele | Lisa Livane | Laurent Ziserman | Benjamin Clery | Mathéo Capelli | Benoit de Gauléjac</t>
+  </si>
+  <si>
+    <t>Le Bureau | Les Compagnons du Cinema | Artémis Productions</t>
+  </si>
+  <si>
+    <t>tt31415482</t>
+  </si>
+  <si>
+    <t>Eleonora Duse</t>
+  </si>
+  <si>
+    <t>Duse</t>
+  </si>
+  <si>
+    <t>Pietro Marcello</t>
+  </si>
+  <si>
+    <t>Valeria Bruni Tedeschi | Fausto Russo Alesi | Fanni Wrochna | Noémie Merlant | Vincenzo Nemolato | Edoardo Sorgente | Gaja Masciale | Vincenza Modica | Mimmo Borrelli | Savino Paparella | Noémie Lvovsky | Vincenzo Pirrotta | Federico Pacifici | Marcello Mazzarella | Giordano Bruno Guerri | Alessio Gorius | Dafne Renate Broglia | Giovanni Morassutti | Emanuele Pesacane | Rita Bosello | Iacopo Fanelli | Vincenzo Iantorno | Nathan Macchioni | Stefano Patti</t>
   </si>
   <si>
     <t>Biography | Drama | History</t>
   </si>
   <si>
-    <t>Focus Features | Davis Entertainment</t>
-  </si>
-  <si>
-    <t>tt21920392</t>
-  </si>
-  <si>
-    <t>Le Secret de l'Angelus, la fascination de Dali</t>
-  </si>
-  <si>
-    <t>El Cas Àngelus. La fascinació de Dalí</t>
-  </si>
-  <si>
-    <t>Joan Frank Charansonnet</t>
-  </si>
-  <si>
-    <t>Joan Frank Charansonnet | Montse Alcoverro | Eduard Alejandre | Joan Massotkleiner | Sílvia Sabaté | Miquel Sitjar | Ricard Balada | Esther Nubiola | Alain Chipot | Júlia Creus | Ramon Godino | Enrique del Pozo | Núria Hosta | Jaume Montané | Montse Ribadellas | Jaume Najarro | Elena Codó | Dodi de Miquel | Elena Antón | Gal Soler | Xavi Prat | Aina Cots | Jordi Pesarrodona | Juna Charansonnet | Gala Charanssonet | Alex Van Whije | Jordi Reverté | Laia Díaz | Guillem Rossell | Dalmau Díaz</t>
-  </si>
-  <si>
-    <t>Comedy | Drama | Thriller</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>No Info</t>
-  </si>
-  <si>
-    <t>3 Pro Entertainment | Patchouli Films | Vivir Rodando</t>
-  </si>
-  <si>
-    <t>tt38777236</t>
-  </si>
-  <si>
-    <t>Vade Retro</t>
-  </si>
-  <si>
-    <t>Antonin Peretjatko</t>
-  </si>
-  <si>
-    <t>Estéban | Pascal Tagnati | Yolène Gontrand | Pascal Légitimus | Céline Fuhrer | Eva Rami | Sébastien Chassagne | Alma Jodorowsky | Arielle Dombasle | Philippe Duquesne | Yuliya Abiss | Athaya Mokonzi | Francis Convert | Fred Tousch | Mao Tao | Laure Le Rouzic | Elica Thiery | Fabienne Guirado | Jacques Deshayes | Cyril Raffaelli | Juliette Satsou | Etienne Thévenin | Loïc Paraveman | David Erudel | Mélanie Seguer | Stéphane Payet | Daniel Luntadi | Antoine Stip | Michel Barr</t>
-  </si>
-  <si>
-    <t>Comedy</t>
-  </si>
-  <si>
-    <t>Acqua Alta | High Sea Production | Kaly Productions</t>
-  </si>
-  <si>
-    <t>tt31648020</t>
-  </si>
-  <si>
-    <t>La dernière valse</t>
-  </si>
-  <si>
-    <t>Po dei juk</t>
-  </si>
-  <si>
-    <t>Anselm Chan</t>
-  </si>
-  <si>
-    <t>Michael Hui | Dayo Wong | Michelle Wai | Pak-Hong Chu | Catherine Chau | Paul Chun | Elaine Jin | Rosa Maria Velasco | Rachel Leung | Michael Ning | Suet-Ying Chung | Thor Lok | Edward Ma | Kiki Cheung | Elly Lam | Polly Lau | Aggie Chow | Chun-Hei Che | Marquis Oakes | Ching-Hin Chan | Katrina Pei Shin Chan | Chor-Ying Chun | Chi-Kui Fong | Vincent Kok | Tsz-Chun Lai | Ling Yuen Lam | Peter Seng-Hin Lee | Lokman Leung | Kit-Wa Li | Ho-Yin Pong</t>
-  </si>
-  <si>
-    <t>Hong Kong</t>
-  </si>
-  <si>
-    <t>Cantonese</t>
-  </si>
-  <si>
-    <t>AMTD Digital | Alibaba Pictures Group | Emperor Motion Pictures</t>
-  </si>
-  <si>
-    <t>tt36456563</t>
-  </si>
-  <si>
-    <t>Magellan</t>
-  </si>
-  <si>
-    <t>Magalhães</t>
-  </si>
-  <si>
-    <t>Lav Diaz</t>
-  </si>
-  <si>
-    <t>Gael García Bernal | Ângela Azevedo | Amado Arjay Babon | Dario Yazbek Bernal | Hazel Orencio | Ronnie Lazaro | Tomás Alves | Bong Cabrera | Rafael Morais | Roger Alan Koza | Valdemar Santos | Brontis Jodorowsky | Ivo Arroja | Paulo Calatré | Max Grosse Majench | Baptiste Pinteaux | Paolo Dumlao | Sasa Cabalquinto | Yvanne Evangelista | Ghdd Amaro | Rafa Siguion-Reyna | Almeno Gonçalves | Rui Serrano | João Fonseca | Cláudio Henriques | Daniel Viana | Erica Rodrigues | Gustavo Caldeira | Mario Huerta | Domingos Countinho</t>
-  </si>
-  <si>
-    <t>Adventure | Biography | Drama</t>
-  </si>
-  <si>
-    <t>Philippines | Spain | Portugal | France | Taiwan</t>
-  </si>
-  <si>
-    <t>Portuguese | English | Spanish | Visayan | French</t>
-  </si>
-  <si>
-    <t>AKP21 | Andergraun Films | Black Cap Pictures</t>
-  </si>
-  <si>
-    <t>tt35465639</t>
-  </si>
-  <si>
-    <t>Le pays d'Arto</t>
-  </si>
-  <si>
-    <t>Tamara Stepanyan</t>
-  </si>
-  <si>
-    <t>Camille Cottin | Zar Amir Ebrahimi | Denis Lavant | Hovnatan Avédikian | Hasmik Suvaryan | Christina Hovaguimyan | Hrach Movsisyan | Haykuhi Khudaverdyan | Gnun Martirosyan | Artur Nersesyan | Thaïs Ferrari Stepanyan | Léon Mahon de Monaghan | Lucie Cottin | Samvel Danielyan | Mkrtich Vardanyan | Edgar Baghdasaryan | Astghik Abajyan | Seda Mkrtchyan | Sona Kankanian | Sergey Eghikyan | Valeri Ghazaryan | Manvel Khachatryan | Arsen Saghatelyan | Khachik Darbinyan | Harut Beg Vanyan | Karina Avetisyan | Susanna Baghdasaryan | Ara J. Movsesian | Samvel Khachatryan | Sasun Sargsyan</t>
-  </si>
-  <si>
-    <t>Armenia | France</t>
-  </si>
-  <si>
-    <t>French | Armenian | English</t>
-  </si>
-  <si>
-    <t>La Huit Production | Pan Cinema | Visan</t>
-  </si>
-  <si>
-    <t>tt31450976</t>
-  </si>
-  <si>
-    <t>Los Tigres</t>
-  </si>
-  <si>
-    <t>Alberto Rodríguez</t>
-  </si>
-  <si>
-    <t>Antonio de la Torre | Bárbara Lennie | Joaquín Núñez | Jesús del Moral | César Vicente | Skone | Silvia Acosta | Marta Correa Radwanska | Fabiola Correa Radwanska | Adrián Ledesma | Claudia Vela | Thimbo Samb | Nico Montoya | Carlos Bernardino | Lupe Cano | Melania Cruz | Numa Paredes | José Antonio Del Moral | José Luis Rasero | Santiago García Martínez | Aixa Pérez | David Guillén | David Palanco | Lorena Ávila | Antonio Estrada | María Dolores Rosa | Joaquín Rodríguez | Adriana Romero | Carmen Llanes | Manuel Navarro Díaz</t>
-  </si>
-  <si>
-    <t>Crime | Thriller</t>
-  </si>
-  <si>
-    <t>Spanish</t>
-  </si>
-  <si>
-    <t>Crea SGR | Diputación de Huelva | Feelgood Media</t>
-  </si>
-  <si>
-    <t>tt36885668</t>
-  </si>
-  <si>
-    <t>Laurent dans le vent</t>
-  </si>
-  <si>
-    <t>Anton Balekdjian | Léo Couture | Mattéo Eustachon</t>
-  </si>
-  <si>
-    <t>Baptiste Perusat | Béatrice Dalle | Thomas Daloz | Monique Crespin | Raymond Barneau | Suzanne De Baecque | Djanis Bouzyani | Lucile Balézeaux | Benoît Glardon | Maxime Magnan | Bruno Leydet | Jonathan Merle | Paméla Lemonier Elias | Virginie Arnaud | Leila Elias | Judith Fraggi | Ira Verbitskaya | François Quiqueré | Joséphine Mourlaque | Louise Pitre | Tommy Baron | René Fouque | Louis Richard</t>
-  </si>
-  <si>
-    <t>Mabel Films | Auvergne Rhône-Alpes Cinéma | Région Provence-Alpes-Côte d'Azur</t>
+    <t>Italy | France</t>
+  </si>
+  <si>
+    <t>Italian</t>
+  </si>
+  <si>
+    <t>Palomar | Avventurosa | Rai Cinema</t>
+  </si>
+  <si>
+    <t>tt14850054</t>
+  </si>
+  <si>
+    <t>Greenland Migration</t>
+  </si>
+  <si>
+    <t>Greenland 2: Migration</t>
+  </si>
+  <si>
+    <t>Ric Roman Waugh</t>
+  </si>
+  <si>
+    <t>Gerard Butler | Morena Baccarin | Tommie Earl Jenkins | Trond Fausa | Amber Rose Revah | Gina Gangar | Antonio De Lima | Peter Polycarpou | Beruce Khan | Roman Griffin Davis | Megan Jacobs Shrivastava | Mitu Panicucci | Gísli Örn Garðarsson | Sidsel Siem Koch | Faraz M. Khan | Nathan Wiley | Gordon Alexander | Alex Lanipekun | Shayn Herndon | Rachael Evelyn | Neil Bell | Andre Squire | Lee Lomas | Ken Nwosu | Sophie Thompson | Xavier Lake | Anthony Knight | William Abadie | Nelia Valery | Susan Eljack</t>
+  </si>
+  <si>
+    <t>Action | Adventure | Sci-Fi</t>
+  </si>
+  <si>
+    <t>Anton | CineMachine Media Works | G-BASE</t>
+  </si>
+  <si>
+    <t>tt31183235</t>
+  </si>
+  <si>
+    <t>Furcy, né libre</t>
+  </si>
+  <si>
+    <t>Abd Al Malik</t>
+  </si>
+  <si>
+    <t>Makita Samba | Romain Duris | Ana Girardot | Vincent Macaigne | Frédéric Pierrot | Micha Lescot | André Marcon | Moussa Mansaly | Liya Kebede | François Sureau | Philippe Torreton | François De Brauer | Michel Bompoil | Emilien Diard-Detoeuf | Xavier de Guillebon | Marie Florestan | Olivier Corista | Caroline Incerti | Camille Léon-Fucien | Matteo Falkone | Didier Brice | Marvin Divo-Prince | Audrey Lévy | Sarah Chaumette | Nans Gourgousse | Sébastien Champagne | Michel Barre | Thibaut Marion | Alban Ramsamy | Liya Bamba Chone</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>Arches Films | Jerico | France 3 Cinéma</t>
+  </si>
+  <si>
+    <t>tt29271622</t>
+  </si>
+  <si>
+    <t>Palestine 36</t>
+  </si>
+  <si>
+    <t>Annemarie Jacir</t>
+  </si>
+  <si>
+    <t>Jeremy Irons | Robert Aramayo | Liam Cunningham | Billy Howle | Hiam Abbass | Christopher Villiers | Yasmine Al Massri | Sam Hoare | Saleh Bakri | Yumna Marwan | Dhafer L'Abidine | Yahya Mahayni | Sofia Asir | Wardi Eilabouni | Nicholas Moss | Joanna Arida | Karim Daoud Anaya | Adam Lawrence | Kamel El Basha | Yafa Bakri | Muhammad Abed Elrahman | George Smale | Jalal Altawil | Aya Khalaf | Areen Omari | Samer Bisharat | Nabil Al Raee | Eyad Hourani | Riyad Sliman | Ula Tabari</t>
+  </si>
+  <si>
+    <t>Occupied Palestinian Territory | UK | USA | France | Denmark | Norway | Qatar | Saudi Arabia | Jordan | Sweden | Australia</t>
+  </si>
+  <si>
+    <t>Arabic | English</t>
+  </si>
+  <si>
+    <t>Philistine Films | Autonomous | Corniche Media</t>
+  </si>
+  <si>
+    <t>tt33290598</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>Elzat Eskendir</t>
+  </si>
+  <si>
+    <t>Yerlan Toleutay | Nurzhan Beksultanova | Alikhan Lepesbaev | Ulan Nusipali</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>tt26731970</t>
+  </si>
+  <si>
+    <t>Jusqu'à l'aube</t>
+  </si>
+  <si>
+    <t>Yoake no subete</t>
+  </si>
+  <si>
+    <t>Shô Miyake</t>
+  </si>
+  <si>
+    <t>Hokuto Matsumura | Mone Kamishiraishi | Sawako Fujima | Haruka Imô | Sonny Mcclendon | Ken Mitsuishi | Ryô | Kiyohiko Shibukawa</t>
+  </si>
+  <si>
+    <t>Asmik Ace Entertainment | Bandai Namco Filmworks | Horipro</t>
+  </si>
+  <si>
+    <t>tt30007864</t>
+  </si>
+  <si>
+    <t>The American Society of Magical Negroes</t>
+  </si>
+  <si>
+    <t>Kobi Libii</t>
+  </si>
+  <si>
+    <t>Justice Smith | Zachary Barton | Anthony Coons | Robbie Troy | Gillian Vigman | James E. Welsh | David Alan Grier | Mia Ford | Eric Lutz | Kees DeVos | Aaron Coleman | Aisha Hinds | Chase Ryan Jeffery | Moe Irvin | Ethan Herisse | Nozipho Mclean | Isayas Theodros | Greg Cohan | Gregor Manns | Toni Youngblood | Reginald James | Jeremiah Birkett | Aaron Jennings | Tim Baltz | Vinny DeGennaro | Nicole Byer | An-Li Bogan | Michaela Watkins | Drew Tarver | Christina Pascucci</t>
+  </si>
+  <si>
+    <t>Comedy | Fantasy</t>
+  </si>
+  <si>
+    <t>USA | Denmark | Canada</t>
+  </si>
+  <si>
+    <t>Sight Unseen Pictures | Focus Features</t>
+  </si>
+  <si>
+    <t>tt37844673</t>
+  </si>
+  <si>
+    <t>Sans pitié</t>
+  </si>
+  <si>
+    <t>Julien Hosmalin</t>
+  </si>
+  <si>
+    <t>Adam Bessa | Tewfik Jallab | Jonathan Turnbull | Laura Sepul | Bérangère McNeese | Wim Willaert | Pascal Elso | Natacha Krief | François Pouron | Frank Williams | Carine Seront | Karim Barras | Benjamin Ramon | Diego Murgia | Claude Semal | Fabrice Boutique | Brigitte Dedry | Laïs Mayyas | Pauline Sakellaridis | Wail Toubeishi | Julian Maerten | Andréa Lopez | Flavie Dachy | Camille Pistone</t>
+  </si>
+  <si>
+    <t>Drama | Thriller</t>
+  </si>
+  <si>
+    <t>France | Belgium</t>
+  </si>
+  <si>
+    <t>Same Player | Les Films du Worso | WTFilms</t>
   </si>
 </sst>
 </file>
@@ -679,11 +724,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="4" max="4" width="14.578125" customWidth="1"/>
-    <col min="7" max="7" width="15.9453125" customWidth="1"/>
+    <col min="1" max="1" width="9.9453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.41796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -744,462 +789,585 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>2024</v>
       </c>
       <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="J2">
-        <v>109</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
       <c r="N2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="O2">
-        <v>182</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
       </c>
       <c r="F3">
         <v>2025</v>
       </c>
       <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3">
+        <v>95</v>
+      </c>
+      <c r="K3" t="s">
         <v>29</v>
       </c>
-      <c r="J3">
-        <v>99</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
       <c r="N3">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="O3">
-        <v>10065</v>
-      </c>
-      <c r="P3">
-        <v>45000000</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <v>2024</v>
+      </c>
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4">
-        <v>2025</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>35</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>83</v>
+      </c>
+      <c r="K4" t="s">
         <v>36</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>37</v>
       </c>
-      <c r="J4">
-        <v>96</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="L4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" t="s">
-        <v>40</v>
-      </c>
       <c r="N4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>2025</v>
       </c>
       <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
         <v>44</v>
       </c>
-      <c r="H5" t="s">
+      <c r="M5" t="s">
         <v>45</v>
       </c>
-      <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5">
-        <v>132</v>
-      </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" t="s">
-        <v>47</v>
-      </c>
       <c r="N5">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="O5">
-        <v>4097</v>
-      </c>
-      <c r="P5">
-        <v>30000000</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
         <v>48</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6">
+        <v>2026</v>
+      </c>
+      <c r="G6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>50</v>
       </c>
-      <c r="F6">
-        <v>2024</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>51</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6">
+        <v>109</v>
+      </c>
+      <c r="K6" t="s">
         <v>52</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>53</v>
       </c>
-      <c r="J6">
-        <v>85</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>54</v>
       </c>
-      <c r="L6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" t="s">
-        <v>56</v>
-      </c>
       <c r="N6">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="O6">
-        <v>25</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7">
         <v>2025</v>
       </c>
       <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>128</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" t="s">
         <v>59</v>
       </c>
-      <c r="H7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" t="s">
-        <v>61</v>
-      </c>
-      <c r="J7">
-        <v>95</v>
-      </c>
-      <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" t="s">
-        <v>62</v>
-      </c>
       <c r="N7">
-        <v>5.0999999999999996</v>
+        <v>7.2</v>
       </c>
       <c r="O7">
-        <v>7</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8">
+        <v>2025</v>
+      </c>
+      <c r="G8" t="s">
         <v>63</v>
       </c>
-      <c r="D8" t="s">
+      <c r="H8" t="s">
         <v>64</v>
       </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
         <v>65</v>
       </c>
-      <c r="F8">
-        <v>2024</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="J8">
+        <v>122</v>
+      </c>
+      <c r="K8" t="s">
         <v>66</v>
       </c>
-      <c r="H8" t="s">
+      <c r="L8" t="s">
         <v>67</v>
       </c>
-      <c r="I8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8">
-        <v>126</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>68</v>
       </c>
-      <c r="L8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" t="s">
-        <v>70</v>
-      </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>3328</v>
+        <v>372</v>
+      </c>
+      <c r="P8">
+        <v>8205753</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
         <v>71</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9">
+        <v>2026</v>
+      </c>
+      <c r="G9" t="s">
         <v>72</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>73</v>
       </c>
-      <c r="F9">
-        <v>2025</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>74</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9">
+        <v>98</v>
+      </c>
+      <c r="K9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" t="s">
         <v>75</v>
       </c>
-      <c r="I9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9">
-        <v>160</v>
-      </c>
-      <c r="K9" t="s">
-        <v>77</v>
-      </c>
-      <c r="L9" t="s">
-        <v>78</v>
-      </c>
-      <c r="M9" t="s">
-        <v>79</v>
-      </c>
       <c r="N9">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="O9">
-        <v>334</v>
+        <v>3318</v>
+      </c>
+      <c r="P9">
+        <v>90000000</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F10">
         <v>2025</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10">
+        <v>109</v>
+      </c>
+      <c r="K10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" t="s">
         <v>37</v>
       </c>
-      <c r="J10">
-        <v>104</v>
-      </c>
-      <c r="K10" t="s">
-        <v>84</v>
-      </c>
-      <c r="L10" t="s">
-        <v>85</v>
-      </c>
       <c r="M10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O10">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="P10">
+        <v>10368000</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F11">
         <v>2025</v>
       </c>
       <c r="G11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="J11">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K11" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="L11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N11">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="O11">
-        <v>403</v>
-      </c>
-      <c r="P11">
-        <v>10800000</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12">
+        <v>2024</v>
+      </c>
+      <c r="G12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12">
+        <v>120</v>
+      </c>
+      <c r="K12" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12">
+        <v>7.2</v>
+      </c>
+      <c r="O12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>94</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>95</v>
       </c>
-      <c r="E12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F12">
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13">
+        <v>2024</v>
+      </c>
+      <c r="G13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H13" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13">
+        <v>119</v>
+      </c>
+      <c r="K13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13">
+        <v>7</v>
+      </c>
+      <c r="O13">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14">
+        <v>2024</v>
+      </c>
+      <c r="G14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14">
+        <v>104</v>
+      </c>
+      <c r="K14" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" t="s">
+        <v>106</v>
+      </c>
+      <c r="N14">
+        <v>3.8</v>
+      </c>
+      <c r="O14">
+        <v>12837</v>
+      </c>
+      <c r="P14">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15">
         <v>2025</v>
       </c>
-      <c r="G12" t="s">
-        <v>96</v>
-      </c>
-      <c r="H12" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12">
+      <c r="G15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" t="s">
         <v>110</v>
       </c>
-      <c r="K12" t="s">
-        <v>38</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" t="s">
-        <v>98</v>
-      </c>
-      <c r="N12">
-        <v>7.4</v>
-      </c>
-      <c r="O12">
-        <v>34</v>
+      <c r="I15" t="s">
+        <v>111</v>
+      </c>
+      <c r="J15">
+        <v>93</v>
+      </c>
+      <c r="K15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" t="s">
+        <v>113</v>
+      </c>
+      <c r="N15">
+        <v>7.9</v>
+      </c>
+      <c r="O15">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/movies_scraped.xlsx
+++ b/movies_scraped.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lione\Desktop\Projets\Cinema_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A30FED-403D-403B-BDEB-B0253CA0B60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF6A441-0BE8-47A8-AF5D-1632E31926ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="11358" windowHeight="12228" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="215">
   <si>
     <t>movie_id</t>
   </si>
@@ -70,298 +70,601 @@
     <t>def_budget</t>
   </si>
   <si>
-    <t>tt32642638</t>
-  </si>
-  <si>
-    <t>Rusalka</t>
-  </si>
-  <si>
-    <t>Claudiu Mitcu</t>
-  </si>
-  <si>
-    <t>Pia Bratianu | Aida Economu | Diana Gheorghian | Claudiu Istodor | Rodica Lazar | Silvana Mihai | Maia Morgenstern | Rodica Negrea | Nelu Serghei | Doina Severin</t>
+    <t>tt38123566</t>
+  </si>
+  <si>
+    <t>With Love</t>
+  </si>
+  <si>
+    <t>Madhan</t>
+  </si>
+  <si>
+    <t>Abishan Jeevinth | Anaswara Rajan | Harish Kumar | Kavya Anil | Theni Murugan | Sacchin Nachiappan | S Rajapandi | Saravanan</t>
+  </si>
+  <si>
+    <t>Comedy | Drama | Romance</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Tamil</t>
+  </si>
+  <si>
+    <t>MRP Entertainment | Soundarya Rajinikanth's Zion Films</t>
+  </si>
+  <si>
+    <t>tt37537155</t>
+  </si>
+  <si>
+    <t>Ashakal Aayiram</t>
+  </si>
+  <si>
+    <t>G. Prajith</t>
+  </si>
+  <si>
+    <t>Jayaram | Kalidas Jayaram | Ishaani Krishna | Anand Manmadhan | Dileep Menon | Akhil Nrd | Ramesh Pisharody | Zhinz Shan | Sharafudheen | Asha Sharath</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>Malayalam</t>
+  </si>
+  <si>
+    <t>Sree Gokulam Movies</t>
+  </si>
+  <si>
+    <t>tt39216314</t>
+  </si>
+  <si>
+    <t>Stray Kids: The dominATE Experience</t>
+  </si>
+  <si>
+    <t>Paul Dugdale | Farah Khalid</t>
+  </si>
+  <si>
+    <t>Bang Chan | Lee Know | Seo Changbin | Hwang Hyun-jin | Han Jisung | Felix Lee | Kim Seungmin | Yang Jeong-in | Stray Kids</t>
+  </si>
+  <si>
+    <t>Documentary | Music</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Live Nation Studios</t>
+  </si>
+  <si>
+    <t>tt27722575</t>
+  </si>
+  <si>
+    <t>200 % Loup</t>
+  </si>
+  <si>
+    <t>200% Wolf</t>
+  </si>
+  <si>
+    <t>Alexs Stadermann</t>
+  </si>
+  <si>
+    <t>Ilai Swindells | Elizabeth Nabben | Jennifer Saunders | Sarah Georgina | Peter McAllum | Samara Weaving | Janice Petersen | Heather Mitchell | Michael Bourchier | Alexs Stadermann | Akmal Saleh | Sarah Harper | Anna Nguyen | Shirley Yao | Matias Biondi | Eden Diebel | Agatha Ozdowska | Tracy Lenon | Jonathan Tappin | Caz Prescott | Virginie Laverdure | Ant Simpson</t>
+  </si>
+  <si>
+    <t>Animation | Action | Adventure</t>
+  </si>
+  <si>
+    <t>Australia | Germany | Spain | Mexico</t>
+  </si>
+  <si>
+    <t>Flying Bark Productions | Atlántika Films | 200 Wolf La Pelicula AIE</t>
+  </si>
+  <si>
+    <t>tt35659725</t>
+  </si>
+  <si>
+    <t>Les Légendaires, le film</t>
+  </si>
+  <si>
+    <t>Les Légendaires</t>
+  </si>
+  <si>
+    <t>Guillaume Ivernel</t>
+  </si>
+  <si>
+    <t>Roman Doduik | Esthèle Dumand | Thomas Sagols | Antoine Schoumsky | Élise Tilloloy | Damien Witecka | Arthur Raynal | Lila Lacombe | Marjorie Frantz | Lucien Jean-Baptiste | Aurélie Konaté | Christophe Lemoine | Bernard Lanneau | Dorothée Pousséo | Penny Padilla | Nathanaël Perrot | Mila Pointet | Isaac Schoumsky | Kendell Byrd | Paul Castro Jr. | Etienne Moana</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>Pan Européenne | Pan Cinema | Belvision</t>
+  </si>
+  <si>
+    <t>tt30959077</t>
+  </si>
+  <si>
+    <t>Le grand Phuket</t>
+  </si>
+  <si>
+    <t>Xiao Ban Jie</t>
+  </si>
+  <si>
+    <t>Yaonan Liu</t>
+  </si>
+  <si>
+    <t>You Junfen | Hang Kang | Li Rongkun | Xuan Yang | Liu Hui Yuan</t>
   </si>
   <si>
     <t>Drama</t>
   </si>
   <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>Romanian | English | Russian</t>
-  </si>
-  <si>
-    <t>tt35487769</t>
-  </si>
-  <si>
-    <t>Alice au pays des merveilles: Dive in Wonderland</t>
-  </si>
-  <si>
-    <t>Fushigi no Kuni de Arisu to Daibu in Wandârando</t>
-  </si>
-  <si>
-    <t>Toshiya Shinohara</t>
-  </si>
-  <si>
-    <t>Nanoka Hara | Maika Pugh | Natsuki Hanae | Subaru Kimura | Ryûichi Kosugi | Shôtarô Mamiya | Mayu Matsuoka | Toshiyuki Morikawa | Ayumu Murase | Yuki Ono | Keiko Toda | Kappei Yamaguchi | Kôji Yamamoto | Takahiro Yamamoto | Norito Yashima</t>
-  </si>
-  <si>
-    <t>Animation | Family | Fantasy</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Japanese</t>
-  </si>
-  <si>
-    <t>P.A. Works | TBS Television</t>
-  </si>
-  <si>
-    <t>tt33035860</t>
-  </si>
-  <si>
-    <t>Les courageux</t>
-  </si>
-  <si>
-    <t>Jasmin Gordon</t>
-  </si>
-  <si>
-    <t>Ophélia Kolb | Jasmine Kalisz Saurer | Paul Besnier | Arthur Devaux | Sabine Timoteo | Roger Bonjour | Claudia Grob | Alexandra Karamisaris | Nabil Rafi | Michel Voïta</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
-  </si>
-  <si>
-    <t>French</t>
-  </si>
-  <si>
-    <t>Maximage</t>
-  </si>
-  <si>
-    <t>tt35932888</t>
-  </si>
-  <si>
-    <t>Forêt rouge</t>
-  </si>
-  <si>
-    <t>Laurie Lassalle</t>
+    <t>Hong Kong | France | Belgium | Germany</t>
+  </si>
+  <si>
+    <t>Mandarin</t>
+  </si>
+  <si>
+    <t>A Private View | Remora Films | Wood Water Films</t>
+  </si>
+  <si>
+    <t>tt35890599</t>
+  </si>
+  <si>
+    <t>N121 - Bus de nuit</t>
+  </si>
+  <si>
+    <t>Morade Aissaoui</t>
+  </si>
+  <si>
+    <t>Riadh Belaïche | Bakary Diombera | Gaspard Gevin-Hié | Paola Locatelli | Aïssatou Diallo Sagna | Arben Bajraktaraj | Mylène Jampanoï | Lucie Charles-Alfred | Laurence Oltuski | Jérémie Covillault | Damien Jouillerot | Azad Boutella | Bounsy Luang Phinith | Beidja Yahiaoui | Audrey Marnay | Louis Duneton | Lahcen Kourkdane | Camille Verschuère | Mauricette Gourdon | Niddal El Mellouhi | Amine Boughanem | Thibault Dyevre | Wissam Toubal | Sofia Ghoul | Abel Mansouri Asselain | Jawad Outoui | Sami Amara | Noémie Desbordes</t>
+  </si>
+  <si>
+    <t>France | Belgium</t>
+  </si>
+  <si>
+    <t>No Info</t>
+  </si>
+  <si>
+    <t>Ripley Films | Cheyenne Federation | Wild Bunch Distribution</t>
+  </si>
+  <si>
+    <t>tt36580119</t>
+  </si>
+  <si>
+    <t>Le gâteau du président</t>
+  </si>
+  <si>
+    <t>Mamlaket al-qasab</t>
+  </si>
+  <si>
+    <t>Hasan Hadi</t>
+  </si>
+  <si>
+    <t>Baneen Ahmad Nayyef | Waheed Thabet Khreibat | Sajad Mohamad Qasem | Muthanna Malaghi | Ahmad Qasem Saywan | Maytham Mreidi | Rahim AlHaj | Thaer Salem | Ali Khalaf | Fatima Abouharoon | Mahmoud Mazen Lazen | Aqeel Wadi | Mohammed Rheimeh | Rokia Alwadi | Ali Saddam Najem | Abdelkarim Jasim | Mohammad Qasem | Raed Harbi Abdeljalil | Elaf Mohamed | Ahmed Al-Hayali | Mohammed Zaid | Al-Hassan Adnan | Mohammed Ammar | Ahmad Hameed Ahmad | Haidar Jamal Jaber | Aqeel Al Shamri | Tayseer Ibrahim Radi | Nadia Rashak</t>
+  </si>
+  <si>
+    <t>Iraq | Qatar | USA</t>
+  </si>
+  <si>
+    <t>Arabic</t>
+  </si>
+  <si>
+    <t>Maiden Voyage Pictures | Missing Piece Films | Spark Features</t>
+  </si>
+  <si>
+    <t>tt31050594</t>
+  </si>
+  <si>
+    <t>Reconnu Coupable</t>
+  </si>
+  <si>
+    <t>Mercy</t>
+  </si>
+  <si>
+    <t>Timur Bekmambetov</t>
+  </si>
+  <si>
+    <t>Chris Pratt | Rebecca Ferguson | Kali Reis | Annabelle Wallis | Chris Sullivan | Kylie Rogers | Jeff Pierre | Rafi Gavron | Kenneth Choi | Jamie McBride | Ross Gosla | Mark Daneri | Haydn Dalton | Michael C. Mahon | Noah Fearnley | Konstantin Podprugin | Cully Pratt | Philicia Saunders | Jay Jackson | Mahmoud Mahmoud | Anja Akstin | Katario Dupreè Young | Evgenia Sinitsin | Richard Cetrone | Renata Ribeiro | Mike Tarnofsky | John Bubniak | Tom Rezvan | Kory Ison | Veronica Rose</t>
+  </si>
+  <si>
+    <t>Action | Crime | Drama</t>
+  </si>
+  <si>
+    <t>Russia | USA</t>
+  </si>
+  <si>
+    <t>Amazon MGM Studios | Atlas Entertainment | Bazelevs Entertainment</t>
+  </si>
+  <si>
+    <t>tt28865633</t>
+  </si>
+  <si>
+    <t>La lumière ne meurt jamais</t>
+  </si>
+  <si>
+    <t>Jossain on valo joka ei sammu</t>
+  </si>
+  <si>
+    <t>Lauri-Matti Parppei</t>
+  </si>
+  <si>
+    <t>Samuel Kujala | Anna Rosaliina Kauno | Camille Auer | Kaisa-Leena Koskenkorva | Mari Rantasila | Jarkko Pajunen | Matti Mustonen</t>
+  </si>
+  <si>
+    <t>Comedy | Drama</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Finnish | English | French</t>
+  </si>
+  <si>
+    <t>Goodtime Pictures | Made</t>
+  </si>
+  <si>
+    <t>tt31557492</t>
+  </si>
+  <si>
+    <t>Les âmes bossales</t>
+  </si>
+  <si>
+    <t>Francois Perlier</t>
   </si>
   <si>
     <t>Documentary</t>
   </si>
   <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>No Info</t>
-  </si>
-  <si>
-    <t>Les Films de l'oeil sauvage | Les Alchimistes | Vià93</t>
-  </si>
-  <si>
-    <t>tt32141377</t>
-  </si>
-  <si>
-    <t>28 ans plus tard: Le temple des morts</t>
-  </si>
-  <si>
-    <t>28 Years Later: The Bone Temple</t>
-  </si>
-  <si>
-    <t>Nia DaCosta</t>
-  </si>
-  <si>
-    <t>Jack O'Connell | Alfie Williams | Connor Newall | Erin Kellyman | Maura Bird | Ghazi Al Ruffai | Robert Rhodes | Emma Laird | Sam Locke | Gareth Locke | Chi Lewis-Parry | Ralph Fiennes | Celi Crossland | Mirren Mack | Gordon Alexander | Louis Ashbourne Serkis | David Sterne | Elliot Benn | Lynne Anne Rodgers | Natalie Cousteau</t>
-  </si>
-  <si>
-    <t>Horror</t>
-  </si>
-  <si>
-    <t>UK | USA</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Columbia Pictures | DNA Films | Decibel Films</t>
-  </si>
-  <si>
-    <t>tt35495035</t>
-  </si>
-  <si>
-    <t>L'affaire Bojarski</t>
-  </si>
-  <si>
-    <t>Jean-Paul Salomé</t>
-  </si>
-  <si>
-    <t>Reda Kateb | Sara Giraudeau | Bastien Bouillon | Pierre Lottin | Quentin Dolmaire | Victor Poirier | Olivier Loustau | Cédric Weber | Camille Japy | Francis Leplay | Arthur Teboul | Lolita Chammah | Margaux Rossi | François Perache | Christophe Kourotchkine | Frédéric Buret | Pierre Giraud | Helena Sadowy | Julien Massetti | Alain Bouzigues | Nicolas Delys | Axelle Simon | Mathieu Thouvenot | Yves Heck | Régis Romele | Lisa Livane | Laurent Ziserman | Benjamin Clery | Mathéo Capelli | Benoit de Gauléjac</t>
-  </si>
-  <si>
-    <t>Le Bureau | Les Compagnons du Cinema | Artémis Productions</t>
-  </si>
-  <si>
-    <t>tt31415482</t>
-  </si>
-  <si>
-    <t>Eleonora Duse</t>
-  </si>
-  <si>
-    <t>Duse</t>
-  </si>
-  <si>
-    <t>Pietro Marcello</t>
-  </si>
-  <si>
-    <t>Valeria Bruni Tedeschi | Fausto Russo Alesi | Fanni Wrochna | Noémie Merlant | Vincenzo Nemolato | Edoardo Sorgente | Gaja Masciale | Vincenza Modica | Mimmo Borrelli | Savino Paparella | Noémie Lvovsky | Vincenzo Pirrotta | Federico Pacifici | Marcello Mazzarella | Giordano Bruno Guerri | Alessio Gorius | Dafne Renate Broglia | Giovanni Morassutti | Emanuele Pesacane | Rita Bosello | Iacopo Fanelli | Vincenzo Iantorno | Nathan Macchioni | Stefano Patti</t>
+    <t>Haiti | France</t>
+  </si>
+  <si>
+    <t>French | Haitian</t>
+  </si>
+  <si>
+    <t>Corpus Films</t>
+  </si>
+  <si>
+    <t>tt33455099</t>
+  </si>
+  <si>
+    <t>The Mastermind</t>
+  </si>
+  <si>
+    <t>Kelly Reichardt</t>
+  </si>
+  <si>
+    <t>Josh O'Connor | Sterling Thompson | Alana Haim | Jasper Thompson | Bill Camp | Hope Davis | Eli Gelb | Cole Doman | Carrie Lazar | Javion Allen | Reighan Bean | Katie Hubbard | Margot Anderson-Song | Avery Deutsch | Deb G. Girdler | Richard Hagerman | Juan Carlos Hernández | Ryan Homchick | Matthew Maher | Marc Ross | Rick Dutrow | Clark Harris | John Magaro | Gaby Hoffmann | Kevin Michael Walsh | Amanda Plummer | Mauricio Soliz | Rhenzy Feliz | Kade Clarks | Mark Antony Howard</t>
+  </si>
+  <si>
+    <t>Crime</t>
+  </si>
+  <si>
+    <t>USA | UK</t>
+  </si>
+  <si>
+    <t>English | French</t>
+  </si>
+  <si>
+    <t>Film Science | MUBI</t>
+  </si>
+  <si>
+    <t>tt29567915</t>
+  </si>
+  <si>
+    <t>Nuremberg</t>
+  </si>
+  <si>
+    <t>James Vanderbilt</t>
+  </si>
+  <si>
+    <t>Rami Malek | Russell Crowe | Michael Shannon | Leo Woodall | John Slattery | Richard E. Grant | Mark O'Brien | Colin Hanks | Wrenn Schmidt | Andreas Pietschmann | Lydia Peckham | Lotte Verbeek | Dieter Riesle | Peter Jordan | Tom Keune | Fleur Bremmer | Ben Miles | Giuseppe Cederna | Paul Antony-Barber | Michael Sheldon | Donald Sage Mackay | Sam Newman | Jeremy Wheeler | Wayne Brett | Blake Kubena | Jonty Peach | Carl Achleitner | Christian Löber | Laurence Pears | Billy Rayner</t>
   </si>
   <si>
     <t>Biography | Drama | History</t>
   </si>
   <si>
-    <t>Italy | France</t>
+    <t>USA | Hungary</t>
+  </si>
+  <si>
+    <t>English | German</t>
+  </si>
+  <si>
+    <t>Walden Media | Filmsquad | Mythology Entertainment</t>
+  </si>
+  <si>
+    <t>tt36599377</t>
+  </si>
+  <si>
+    <t>La vie après Siham</t>
+  </si>
+  <si>
+    <t>Namir Abdel Messeeh</t>
+  </si>
+  <si>
+    <t>Waguih Abdel Messeeh | Namir Abdel Messeeh</t>
+  </si>
+  <si>
+    <t>France | Egypt</t>
+  </si>
+  <si>
+    <t>Oweda Films | Les Films d'Ici | Ambient Light</t>
+  </si>
+  <si>
+    <t>tt33029380</t>
+  </si>
+  <si>
+    <t>Marsupilami</t>
+  </si>
+  <si>
+    <t>Philippe Lacheau</t>
+  </si>
+  <si>
+    <t>Philippe Lacheau | Jamel Debbouze | Tarek Boudali | Élodie Fontan | Julien Arruti | Alban Ivanov | Corentin Guillot | Reem Kherici | Jean Reno | Gérard Jugnot | Didier Bourdon | Paco Boisson | Jamel Elgharbi | Catherine Giron | Kamel Laadaili | Adeline Tayoro | Alexandros Giannou | Youssef Sahraoui | Arthur Sanigou | Hassen Boubritou | Laurent Spielvogel | Jean-Philippe Paravisini | Enlil Albanna | Alexis Boucot | Vincent Desagnat | Nathalie Kent | Cédric Rigaut | Booder | Romain Lancry | David Faure</t>
+  </si>
+  <si>
+    <t>Adventure | Comedy | Family</t>
+  </si>
+  <si>
+    <t>Pathé | Baf Prod | TF1 Films Production</t>
+  </si>
+  <si>
+    <t>tt31777964</t>
+  </si>
+  <si>
+    <t>Gourou</t>
+  </si>
+  <si>
+    <t>Yann Gozlan</t>
+  </si>
+  <si>
+    <t>Pierre Niney | Marion Barbeau | Anthony Bajon | Christophe Montenez | Jonathan Turnbull | Raphaëlle Simon | Tracy Gotoas | Holt McCallany | Léonie Simaga | Manon Kneusé | Paul Scarfoglio | Deborah Grall | Leanna Chea | Mazigh Bouaich | Eric Khanthavixay | Sonia Imbert | César Méric | Céline Carrère | Éric Naggar | Elric Covarel Garcia | Alexandre Malesson | Alex Elliott | Laurie Catherine Winkel | Charlotte Houdin | Youri Lauriette | Zoé Garcia | Costa Canda | Abdallah Charki | Lenni Prezelin | Paco Fuster</t>
+  </si>
+  <si>
+    <t>Thriller</t>
+  </si>
+  <si>
+    <t>Wy Productions | Ninety Films | StudioCanal</t>
+  </si>
+  <si>
+    <t>tt29612071</t>
+  </si>
+  <si>
+    <t>Biscuit le chien fantastique</t>
+  </si>
+  <si>
+    <t>Charlie the Wonderdog</t>
+  </si>
+  <si>
+    <t>Shea Wageman</t>
+  </si>
+  <si>
+    <t>Owen Wilson | Tabitha St. Germain | Sebastian Billingsley-Rodriguez | Rhona Rees | Caitlynne Medrek | Ruairi MacDonald | Anthony Bolognese | Emily Delahunty | David Dixon | Jenn Rogan | Mela Pietropaolo | Lindsay Gibson | Dawson Littman | Zac Bennett-McPhee</t>
+  </si>
+  <si>
+    <t>Animation | Comedy | Family</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>ICON Creative Studio | Centurion Pictures</t>
+  </si>
+  <si>
+    <t>tt33311007</t>
+  </si>
+  <si>
+    <t>Promis le ciel</t>
+  </si>
+  <si>
+    <t>Erige Sehiri</t>
+  </si>
+  <si>
+    <t>Aïssa Maïga | Laetitia Ky | Debora Lobe Naney | Mohamed Grayaâ | Foued Zaazaa | Estelle Kenza Dpgbo | Touré Blamassi | Roxanne Takouri | Marie-Noël Ngwe | Elisabeth Kongolo Badibanga | Zohe Malunda | Elly Franck Biboum | David Emmanuel Biboum | Yate Amos Bebo | Viviane Boudouaahou | Kouakou William Konan | Yao Koff Siméon | Charlotte Ourega | Flora Bozoua | Jean Claude Yué | Christ Jordan</t>
+  </si>
+  <si>
+    <t>Tunisia | France | Qatar</t>
+  </si>
+  <si>
+    <t>Arabic | French</t>
+  </si>
+  <si>
+    <t>Maneki Films | Henia Production | Canal+</t>
+  </si>
+  <si>
+    <t>tt33616511</t>
+  </si>
+  <si>
+    <t>Bel Ami</t>
+  </si>
+  <si>
+    <t>Piao liang peng you</t>
+  </si>
+  <si>
+    <t>Jun Geng</t>
+  </si>
+  <si>
+    <t>Xuanyu Chen | Qing Wang | Zixing Wang | Gang Xu | Baohe Xue | Liguo Yuan | Zhiyong Zhang</t>
+  </si>
+  <si>
+    <t>France | China</t>
+  </si>
+  <si>
+    <t>Chinese | English</t>
+  </si>
+  <si>
+    <t>Blackfin Production</t>
+  </si>
+  <si>
+    <t>tt34886821</t>
+  </si>
+  <si>
+    <t>La grazia</t>
+  </si>
+  <si>
+    <t>Paolo Sorrentino</t>
+  </si>
+  <si>
+    <t>Toni Servillo | Anna Ferzetti | Orlando Cinque | Massimo Venturiello | Milvia Marigliano | Giuseppe Gaiani | Giovanna Guida | Alessia Giuliani | Roberto Zibetti | Vasco Mirandola | Linda Messerklinger | Rufin Doh Zeyenouin | Simone Colombari | Alexandra Gottschlich | Lucio Zagaria | Francesco Martino | Tommaso Amadio | Guè Pequeno | Shablo | Fabrizio Bordignon | Alessandro Salvatori | Michele Azzarito | Elisa Perolini | Giorgia Liguori | Cesare Scova | Giulio Prosperi | Ernesto Caccetta | Alessia Santini | Stefania Barca | Federica Corti</t>
+  </si>
+  <si>
+    <t>Italy</t>
   </si>
   <si>
     <t>Italian</t>
   </si>
   <si>
-    <t>Palomar | Avventurosa | Rai Cinema</t>
-  </si>
-  <si>
-    <t>tt14850054</t>
-  </si>
-  <si>
-    <t>Greenland Migration</t>
-  </si>
-  <si>
-    <t>Greenland 2: Migration</t>
-  </si>
-  <si>
-    <t>Ric Roman Waugh</t>
-  </si>
-  <si>
-    <t>Gerard Butler | Morena Baccarin | Tommie Earl Jenkins | Trond Fausa | Amber Rose Revah | Gina Gangar | Antonio De Lima | Peter Polycarpou | Beruce Khan | Roman Griffin Davis | Megan Jacobs Shrivastava | Mitu Panicucci | Gísli Örn Garðarsson | Sidsel Siem Koch | Faraz M. Khan | Nathan Wiley | Gordon Alexander | Alex Lanipekun | Shayn Herndon | Rachael Evelyn | Neil Bell | Andre Squire | Lee Lomas | Ken Nwosu | Sophie Thompson | Xavier Lake | Anthony Knight | William Abadie | Nelia Valery | Susan Eljack</t>
-  </si>
-  <si>
-    <t>Action | Adventure | Sci-Fi</t>
-  </si>
-  <si>
-    <t>Anton | CineMachine Media Works | G-BASE</t>
-  </si>
-  <si>
-    <t>tt31183235</t>
-  </si>
-  <si>
-    <t>Furcy, né libre</t>
-  </si>
-  <si>
-    <t>Abd Al Malik</t>
-  </si>
-  <si>
-    <t>Makita Samba | Romain Duris | Ana Girardot | Vincent Macaigne | Frédéric Pierrot | Micha Lescot | André Marcon | Moussa Mansaly | Liya Kebede | François Sureau | Philippe Torreton | François De Brauer | Michel Bompoil | Emilien Diard-Detoeuf | Xavier de Guillebon | Marie Florestan | Olivier Corista | Caroline Incerti | Camille Léon-Fucien | Matteo Falkone | Didier Brice | Marvin Divo-Prince | Audrey Lévy | Sarah Chaumette | Nans Gourgousse | Sébastien Champagne | Michel Barre | Thibaut Marion | Alban Ramsamy | Liya Bamba Chone</t>
-  </si>
-  <si>
-    <t>History</t>
-  </si>
-  <si>
-    <t>Arches Films | Jerico | France 3 Cinéma</t>
-  </si>
-  <si>
-    <t>tt29271622</t>
-  </si>
-  <si>
-    <t>Palestine 36</t>
-  </si>
-  <si>
-    <t>Annemarie Jacir</t>
-  </si>
-  <si>
-    <t>Jeremy Irons | Robert Aramayo | Liam Cunningham | Billy Howle | Hiam Abbass | Christopher Villiers | Yasmine Al Massri | Sam Hoare | Saleh Bakri | Yumna Marwan | Dhafer L'Abidine | Yahya Mahayni | Sofia Asir | Wardi Eilabouni | Nicholas Moss | Joanna Arida | Karim Daoud Anaya | Adam Lawrence | Kamel El Basha | Yafa Bakri | Muhammad Abed Elrahman | George Smale | Jalal Altawil | Aya Khalaf | Areen Omari | Samer Bisharat | Nabil Al Raee | Eyad Hourani | Riyad Sliman | Ula Tabari</t>
-  </si>
-  <si>
-    <t>Occupied Palestinian Territory | UK | USA | France | Denmark | Norway | Qatar | Saudi Arabia | Jordan | Sweden | Australia</t>
-  </si>
-  <si>
-    <t>Arabic | English</t>
-  </si>
-  <si>
-    <t>Philistine Films | Autonomous | Corniche Media</t>
-  </si>
-  <si>
-    <t>tt33290598</t>
-  </si>
-  <si>
-    <t>Abel</t>
-  </si>
-  <si>
-    <t>Elzat Eskendir</t>
-  </si>
-  <si>
-    <t>Yerlan Toleutay | Nurzhan Beksultanova | Alikhan Lepesbaev | Ulan Nusipali</t>
-  </si>
-  <si>
-    <t>Kazakhstan</t>
-  </si>
-  <si>
-    <t>tt26731970</t>
-  </si>
-  <si>
-    <t>Jusqu'à l'aube</t>
-  </si>
-  <si>
-    <t>Yoake no subete</t>
-  </si>
-  <si>
-    <t>Shô Miyake</t>
-  </si>
-  <si>
-    <t>Hokuto Matsumura | Mone Kamishiraishi | Sawako Fujima | Haruka Imô | Sonny Mcclendon | Ken Mitsuishi | Ryô | Kiyohiko Shibukawa</t>
-  </si>
-  <si>
-    <t>Asmik Ace Entertainment | Bandai Namco Filmworks | Horipro</t>
-  </si>
-  <si>
-    <t>tt30007864</t>
-  </si>
-  <si>
-    <t>The American Society of Magical Negroes</t>
-  </si>
-  <si>
-    <t>Kobi Libii</t>
-  </si>
-  <si>
-    <t>Justice Smith | Zachary Barton | Anthony Coons | Robbie Troy | Gillian Vigman | James E. Welsh | David Alan Grier | Mia Ford | Eric Lutz | Kees DeVos | Aaron Coleman | Aisha Hinds | Chase Ryan Jeffery | Moe Irvin | Ethan Herisse | Nozipho Mclean | Isayas Theodros | Greg Cohan | Gregor Manns | Toni Youngblood | Reginald James | Jeremiah Birkett | Aaron Jennings | Tim Baltz | Vinny DeGennaro | Nicole Byer | An-Li Bogan | Michaela Watkins | Drew Tarver | Christina Pascucci</t>
-  </si>
-  <si>
-    <t>Comedy | Fantasy</t>
-  </si>
-  <si>
-    <t>USA | Denmark | Canada</t>
-  </si>
-  <si>
-    <t>Sight Unseen Pictures | Focus Features</t>
-  </si>
-  <si>
-    <t>tt37844673</t>
-  </si>
-  <si>
-    <t>Sans pitié</t>
-  </si>
-  <si>
-    <t>Julien Hosmalin</t>
-  </si>
-  <si>
-    <t>Adam Bessa | Tewfik Jallab | Jonathan Turnbull | Laura Sepul | Bérangère McNeese | Wim Willaert | Pascal Elso | Natacha Krief | François Pouron | Frank Williams | Carine Seront | Karim Barras | Benjamin Ramon | Diego Murgia | Claude Semal | Fabrice Boutique | Brigitte Dedry | Laïs Mayyas | Pauline Sakellaridis | Wail Toubeishi | Julian Maerten | Andréa Lopez | Flavie Dachy | Camille Pistone</t>
-  </si>
-  <si>
-    <t>Drama | Thriller</t>
-  </si>
-  <si>
-    <t>France | Belgium</t>
-  </si>
-  <si>
-    <t>Same Player | Les Films du Worso | WTFilms</t>
+    <t>The Apartment | Numero 10 | PiperFilm</t>
+  </si>
+  <si>
+    <t>tt32558601</t>
+  </si>
+  <si>
+    <t>Baise-en-ville</t>
+  </si>
+  <si>
+    <t>Martin Jauvat</t>
+  </si>
+  <si>
+    <t>Martin Jauvat | Emmanuelle Bercot | William Lebghil | Sébastien Chassagne | Anaïde Rozam | Michel Hazanavicius | Mahaut Adam | Annabelle Lengronne | Eva Huault | Aurélien Bellanger | Géraldine Pailhas | Georges Pillegand | Louise Blachère | Erwin Aureillan | Jean-Luc Vincent | Ferdinand Niquet-Rioux | Mike Bujoli | Marlon Macias | Mélanie Bourgeois | Mahamadou Sangaré | Nicolas Delys | Inès Dumont | Akira Seto-Chaumet</t>
+  </si>
+  <si>
+    <t>Comedy</t>
+  </si>
+  <si>
+    <t>Ecce Films | France 2 Cinéma | Netflix</t>
+  </si>
+  <si>
+    <t>tt35932382</t>
+  </si>
+  <si>
+    <t>À demain sur la lune</t>
+  </si>
+  <si>
+    <t>Thomas Balmès</t>
+  </si>
+  <si>
+    <t>Hassen Bouchakour</t>
+  </si>
+  <si>
+    <t>TBC Productions</t>
+  </si>
+  <si>
+    <t>tt22868010</t>
+  </si>
+  <si>
+    <t>Retour à Silent Hill</t>
+  </si>
+  <si>
+    <t>Return to Silent Hill</t>
+  </si>
+  <si>
+    <t>Christophe Gans</t>
+  </si>
+  <si>
+    <t>Jeremy Irvine | Hannah Emily Anderson | Robert Strange | Ljiljana Velimirov | Giulia Pelagatti | Evie Templeton | Pearse Egan | Eve Macklin | Emily Carding | Nicola Alexis | Martine Richards | Howard Saddler | Matteo Pasquini | Melissa Graham | Lara Duru | Karya Duru | Alana Maria | Rhiannon Moushall | Slavisa Ivanovic | Adam Basil | Masa Anic | Ljudmila Korobova | Ana Obradovic | Anastasija Kanazarevic | Marija Milicevic | Tamara Ristoska | Jasper Salon | Sandy E. Scott</t>
+  </si>
+  <si>
+    <t>Drama | Horror | Mystery</t>
+  </si>
+  <si>
+    <t>France | USA | UK | Germany | Serbia | Japan</t>
+  </si>
+  <si>
+    <t>Davis Films | The Electric Shadow Company | Supernix</t>
+  </si>
+  <si>
+    <t>tt37660587</t>
+  </si>
+  <si>
+    <t>À pied d'œuvre</t>
+  </si>
+  <si>
+    <t>À pied d'oeuvre</t>
+  </si>
+  <si>
+    <t>Valérie Donzelli</t>
+  </si>
+  <si>
+    <t>Adrien Barazzone | Valérie Donzelli | Claude Perron | Béatrice de Staël | Mamadou Diallo | Thelma Pourias | Oscar Tillette | Eve Oron | Marion Lecrivain | Benoît Carre | Ahlam Slama | Hélène Rimenaid | Clémence Coullon | Carmen Kouyaté | Pauline Serieys | Sacha Wintz | Rei Watanabe | Maly Diallo | Michel Gondry | Pauline Fugaldi | Éric Reinhardt | Marie Aubrun | Christopher Thompson | Naëlle Dariya | Jérémie Laure | Marion Jadot | Benjamin Clery | Franc Bruneau | Isabelle Goev | Soufiane Sarr</t>
+  </si>
+  <si>
+    <t>Biography | Drama</t>
+  </si>
+  <si>
+    <t>Pitchipoï Productions | France 2 Cinéma | Canal+</t>
+  </si>
+  <si>
+    <t>tt32263650</t>
+  </si>
+  <si>
+    <t>Christy and His Brother</t>
+  </si>
+  <si>
+    <t>Christy</t>
+  </si>
+  <si>
+    <t>Brendan Canty</t>
+  </si>
+  <si>
+    <t>Danny Power | Diarmuid Noyes | AJ Brown | Arla Brown | Emma Willis | Darren Stewart | Jamie Forde | Cara Cullen | Sophie McNamara | Ciaran Bermingham | Chris Walley | Kane O'Connell O'Flynn | Taylor Lee-Keating | Ciaran McCarthy | Lewis Brophy | Aaron Katambay | Alison Oliver | Charleigh Bailey | Ian Tabone | Rúaidhrí Conroy | Hilary Vesey | Keano Power | Tim Roche | Helen Behan | Garry McCarthy | Sophie McCarthy | Christine McSweeney | Jordan Kelly | Michael O'Donoghue | Aaron Hayes</t>
+  </si>
+  <si>
+    <t>Ireland | UK</t>
+  </si>
+  <si>
+    <t>BBC Film | Fís Éireann / Screen Ireland | Sleeper Films</t>
+  </si>
+  <si>
+    <t>tt31710990</t>
+  </si>
+  <si>
+    <t>Dreams</t>
+  </si>
+  <si>
+    <t>Michel Franco</t>
+  </si>
+  <si>
+    <t>Isaac Hernández | Eduardo Gonzalez | Hugo Costa Ramos | Julio Bernal | René Martínez | Nadia Chiney | Jessica Chastain | Rupert Friend | Marshall Bell | Nadia Flamenco | Ali Kiley | Areyla Faeron | Rafael Jiménez | Mercedes Hernández | Eligio Meléndez | Ana Echeverría | Azarel Govea | Brenda Alardín | Bryant Pineda | Camila Medellín | Carla Benassini | Germán Martínez | Helena Alonso | Jimena Esqueda Hernández | Karen Breidsprecher Wong | Leonardo Puchet | Mariana Arroyo Tinoco | Sinuhé Villalón | Martha Elena Trejo O'reilly | Magali Hernández</t>
+  </si>
+  <si>
+    <t>Drama | Romance | Thriller</t>
+  </si>
+  <si>
+    <t>USA | Mexico</t>
+  </si>
+  <si>
+    <t>English | Spanish</t>
+  </si>
+  <si>
+    <t>Teorema | Freckle Films | AR Content</t>
+  </si>
+  <si>
+    <t>tt14142060</t>
+  </si>
+  <si>
+    <t>Rental Family</t>
+  </si>
+  <si>
+    <t>Hikari</t>
+  </si>
+  <si>
+    <t>Brendan Fraser | Paolo Andrea Di Pietro | Shinji Ozeki | Takao Kin | Risa Kameda | Yuma Sonan | Kana Kitty | Gan Furukawa | Yuji Komatsu | Ryôko Osada | Helen Sadler | Kaoru Mizuki | Takehiro Hira | Mari Yamamoto | Shôhei Uno | Sonoe Mizoguchi | Keiji Yamashita | Kimura Bun | Yuki Kimura | Tsutomu Osabe | Rei Yukinaga | Shiho Asami | Seiga | Kazue Oda | Misato Morita | Daikichi Sugawara | Hideko Hara | Nanami Kawakami | Tamae Andô | Kan Kobayashi</t>
+  </si>
+  <si>
+    <t>Japan | USA</t>
+  </si>
+  <si>
+    <t>English | Japanese</t>
+  </si>
+  <si>
+    <t>Knockonwood | Domo Arigato Productions | Sight Unseen Pictures</t>
   </si>
 </sst>
 </file>
@@ -724,11 +1027,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="9.9453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.41796875" customWidth="1"/>
+    <col min="1" max="1" width="12.578125" customWidth="1"/>
+    <col min="4" max="4" width="25.89453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -792,7 +1095,7 @@
         <v>17</v>
       </c>
       <c r="F2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -804,7 +1107,7 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
@@ -812,25 +1115,28 @@
       <c r="L2" t="s">
         <v>22</v>
       </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
       <c r="N2">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
       </c>
       <c r="F3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
@@ -842,48 +1148,48 @@
         <v>28</v>
       </c>
       <c r="J3">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
         <v>29</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>30</v>
       </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
       <c r="N3">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4">
+        <v>2026</v>
+      </c>
+      <c r="G4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4">
-        <v>2024</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>35</v>
       </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
       <c r="J4">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="K4" t="s">
         <v>36</v>
@@ -895,10 +1201,10 @@
         <v>38</v>
       </c>
       <c r="N4">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -909,63 +1215,66 @@
         <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N5">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="O5">
-        <v>5</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J6">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="K6" t="s">
         <v>52</v>
@@ -977,10 +1286,10 @@
         <v>54</v>
       </c>
       <c r="N6">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="O6">
-        <v>7899</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -991,383 +1300,913 @@
         <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J7">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="K7" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="M7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N7">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="O7">
-        <v>91</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J8">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="K8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O8">
-        <v>372</v>
-      </c>
-      <c r="P8">
-        <v>8205753</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="J9">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K9" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L9" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="M9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N9">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="O9">
-        <v>3318</v>
-      </c>
-      <c r="P9">
-        <v>90000000</v>
+        <v>724</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J10">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="L10" t="s">
         <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O10">
-        <v>41</v>
+        <v>9520</v>
       </c>
       <c r="P10">
-        <v>10368000</v>
+        <v>60000000</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F11">
         <v>2025</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="J11">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L11" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M11" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="N11">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="O11">
-        <v>4653</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F12">
         <v>2024</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="K12" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>101</v>
+      </c>
+      <c r="M12" t="s">
+        <v>102</v>
       </c>
       <c r="N12">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="O12">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F13">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H13" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="J13">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="K13" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="O13">
-        <v>956</v>
+        <v>10007</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14">
+        <v>111</v>
+      </c>
+      <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F14">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G14" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="H14" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="J14">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="K14" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N14">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="O14">
-        <v>12837</v>
-      </c>
-      <c r="P14">
-        <v>15000000</v>
+        <v>57125</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F15">
         <v>2025</v>
       </c>
       <c r="G15" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" t="s">
+        <v>99</v>
+      </c>
+      <c r="J15">
+        <v>76</v>
+      </c>
+      <c r="K15" t="s">
+        <v>123</v>
+      </c>
+      <c r="L15" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" t="s">
+        <v>124</v>
+      </c>
+      <c r="N15">
+        <v>6.9</v>
+      </c>
+      <c r="O15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16">
+        <v>2025</v>
+      </c>
+      <c r="G16" t="s">
+        <v>127</v>
+      </c>
+      <c r="H16" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" t="s">
+        <v>129</v>
+      </c>
+      <c r="J16">
+        <v>99</v>
+      </c>
+      <c r="K16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M16" t="s">
+        <v>130</v>
+      </c>
+      <c r="N16">
+        <v>6.2</v>
+      </c>
+      <c r="O16">
+        <v>180</v>
+      </c>
+      <c r="P16">
+        <v>30974400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17">
+        <v>2025</v>
+      </c>
+      <c r="G17" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17">
+        <v>126</v>
+      </c>
+      <c r="K17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" t="s">
+        <v>136</v>
+      </c>
+      <c r="N17">
+        <v>6.4</v>
+      </c>
+      <c r="O17">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="F18">
+        <v>2025</v>
+      </c>
+      <c r="G18" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18">
+        <v>95</v>
+      </c>
+      <c r="K18" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" t="s">
+        <v>144</v>
+      </c>
+      <c r="N18">
+        <v>5.4</v>
+      </c>
+      <c r="O18">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19">
+        <v>2025</v>
+      </c>
+      <c r="G19" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" t="s">
+        <v>148</v>
+      </c>
+      <c r="I19" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19">
+        <v>92</v>
+      </c>
+      <c r="K19" t="s">
+        <v>149</v>
+      </c>
+      <c r="L19" t="s">
+        <v>150</v>
+      </c>
+      <c r="M19" t="s">
+        <v>151</v>
+      </c>
+      <c r="N19">
+        <v>6.5</v>
+      </c>
+      <c r="O19">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>152</v>
+      </c>
+      <c r="D20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20">
+        <v>2024</v>
+      </c>
+      <c r="G20" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" t="s">
+        <v>156</v>
+      </c>
+      <c r="I20" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20">
+        <v>117</v>
+      </c>
+      <c r="K20" t="s">
+        <v>157</v>
+      </c>
+      <c r="L20" t="s">
+        <v>158</v>
+      </c>
+      <c r="M20" t="s">
+        <v>159</v>
+      </c>
+      <c r="N20">
+        <v>7.2</v>
+      </c>
+      <c r="O20">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21">
+        <v>2025</v>
+      </c>
+      <c r="G21" t="s">
+        <v>162</v>
+      </c>
+      <c r="H21" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21" t="s">
+        <v>60</v>
+      </c>
+      <c r="J21">
+        <v>133</v>
+      </c>
+      <c r="K21" t="s">
+        <v>164</v>
+      </c>
+      <c r="L21" t="s">
+        <v>165</v>
+      </c>
+      <c r="M21" t="s">
+        <v>166</v>
+      </c>
+      <c r="N21">
+        <v>7.4</v>
+      </c>
+      <c r="O21">
+        <v>3095</v>
+      </c>
+      <c r="P21">
+        <v>22506151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>167</v>
+      </c>
+      <c r="D22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" t="s">
+        <v>168</v>
+      </c>
+      <c r="F22">
+        <v>2025</v>
+      </c>
+      <c r="G22" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" t="s">
+        <v>170</v>
+      </c>
+      <c r="I22" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22">
+        <v>97</v>
+      </c>
+      <c r="K22" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" t="s">
+        <v>172</v>
+      </c>
+      <c r="N22">
+        <v>6.5</v>
+      </c>
+      <c r="O22">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>173</v>
+      </c>
+      <c r="D23" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23">
+        <v>2025</v>
+      </c>
+      <c r="G23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" t="s">
+        <v>176</v>
+      </c>
+      <c r="I23" t="s">
+        <v>99</v>
+      </c>
+      <c r="J23">
+        <v>80</v>
+      </c>
+      <c r="K23" t="s">
+        <v>52</v>
+      </c>
+      <c r="L23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" t="s">
+        <v>177</v>
+      </c>
+      <c r="N23">
+        <v>7.1</v>
+      </c>
+      <c r="O23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24">
+        <v>2026</v>
+      </c>
+      <c r="G24" t="s">
+        <v>181</v>
+      </c>
+      <c r="H24" t="s">
+        <v>182</v>
+      </c>
+      <c r="I24" t="s">
+        <v>183</v>
+      </c>
+      <c r="J24">
+        <v>106</v>
+      </c>
+      <c r="K24" t="s">
+        <v>184</v>
+      </c>
+      <c r="L24" t="s">
+        <v>37</v>
+      </c>
+      <c r="M24" t="s">
+        <v>185</v>
+      </c>
+      <c r="N24">
+        <v>4.2</v>
+      </c>
+      <c r="O24">
+        <v>7252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" t="s">
+        <v>188</v>
+      </c>
+      <c r="F25">
+        <v>2025</v>
+      </c>
+      <c r="G25" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" t="s">
+        <v>190</v>
+      </c>
+      <c r="I25" t="s">
+        <v>191</v>
+      </c>
+      <c r="J25">
+        <v>92</v>
+      </c>
+      <c r="K25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" t="s">
+        <v>192</v>
+      </c>
+      <c r="N25">
+        <v>6.9</v>
+      </c>
+      <c r="O25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>193</v>
+      </c>
+      <c r="D26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26">
+        <v>2025</v>
+      </c>
+      <c r="G26" t="s">
+        <v>196</v>
+      </c>
+      <c r="H26" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" t="s">
+        <v>60</v>
+      </c>
+      <c r="J26">
+        <v>94</v>
+      </c>
+      <c r="K26" t="s">
+        <v>198</v>
+      </c>
+      <c r="L26" t="s">
+        <v>37</v>
+      </c>
+      <c r="M26" t="s">
+        <v>199</v>
+      </c>
+      <c r="N26">
+        <v>7.4</v>
+      </c>
+      <c r="O26">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" t="s">
+        <v>201</v>
+      </c>
+      <c r="F27">
+        <v>2025</v>
+      </c>
+      <c r="G27" t="s">
+        <v>202</v>
+      </c>
+      <c r="H27" t="s">
+        <v>203</v>
+      </c>
+      <c r="I27" t="s">
+        <v>204</v>
+      </c>
+      <c r="J27">
+        <v>95</v>
+      </c>
+      <c r="K27" t="s">
+        <v>205</v>
+      </c>
+      <c r="L27" t="s">
+        <v>206</v>
+      </c>
+      <c r="M27" t="s">
+        <v>207</v>
+      </c>
+      <c r="N27">
+        <v>5.7</v>
+      </c>
+      <c r="O27">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28">
+        <v>2025</v>
+      </c>
+      <c r="G28" t="s">
+        <v>210</v>
+      </c>
+      <c r="H28" t="s">
+        <v>211</v>
+      </c>
+      <c r="I28" t="s">
+        <v>92</v>
+      </c>
+      <c r="J28">
         <v>109</v>
       </c>
-      <c r="H15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I15" t="s">
-        <v>111</v>
-      </c>
-      <c r="J15">
-        <v>93</v>
-      </c>
-      <c r="K15" t="s">
-        <v>112</v>
-      </c>
-      <c r="L15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" t="s">
-        <v>113</v>
-      </c>
-      <c r="N15">
-        <v>7.9</v>
-      </c>
-      <c r="O15">
-        <v>35</v>
+      <c r="K28" t="s">
+        <v>212</v>
+      </c>
+      <c r="L28" t="s">
+        <v>213</v>
+      </c>
+      <c r="M28" t="s">
+        <v>214</v>
+      </c>
+      <c r="N28">
+        <v>7.6</v>
+      </c>
+      <c r="O28">
+        <v>26912</v>
       </c>
     </row>
   </sheetData>

--- a/movies_scraped.xlsx
+++ b/movies_scraped.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lione\Desktop\Projets\Cinema_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF6A441-0BE8-47A8-AF5D-1632E31926ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C83FF1-7DB7-4851-A974-A9A95DB98EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="242">
   <si>
     <t>movie_id</t>
   </si>
@@ -70,601 +81,682 @@
     <t>def_budget</t>
   </si>
   <si>
-    <t>tt38123566</t>
-  </si>
-  <si>
-    <t>With Love</t>
-  </si>
-  <si>
-    <t>Madhan</t>
-  </si>
-  <si>
-    <t>Abishan Jeevinth | Anaswara Rajan | Harish Kumar | Kavya Anil | Theni Murugan | Sacchin Nachiappan | S Rajapandi | Saravanan</t>
+    <t>tt35404853</t>
+  </si>
+  <si>
+    <t>Ceux qui comptent</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste Léonetti</t>
+  </si>
+  <si>
+    <t>Sandrine Kiberlain | Pierre Lottin | Louise Labèque | Alexis Rosenstiehl | Alma Ngoc | Melissa Izquierdo | Mogamed Bechiev | Frans Boyer | Matthieu Jordan | Olivier-Pierre Richard | Florent Bigot de Nesles | Louise Charnalet | Bruno Paviot | Quitterie Picamoles | Kevin Marvinio | Robert Moundi | Philéas Bourdon | Lucas El Bali | Dune Miki | Lison Thébault | Laura Mounier | Ianis Bonnel | Mila Besson | Marie Laparra</t>
+  </si>
+  <si>
+    <t>Comedy | Drama</t>
+  </si>
+  <si>
+    <t>No Info</t>
+  </si>
+  <si>
+    <t>Les films du 24 | France 2 Cinéma | Entourage Sofica 4</t>
+  </si>
+  <si>
+    <t>tt33549447</t>
+  </si>
+  <si>
+    <t>Anemone - Les racines du mensonge</t>
+  </si>
+  <si>
+    <t>Anemone</t>
+  </si>
+  <si>
+    <t>Ronan Day-Lewis</t>
+  </si>
+  <si>
+    <t>Sean Bean | Samuel Bottomley | Lewis Ian Bray | Paul Butterworth | Karl Cam | JP Conway | Angus Cooper | Daniel Day-Lewis | Adam Fogerty | Richard Graham | Mark Holgate | Samantha Morton | Safia Oakley-Green | Holly Rhys | Jag Sanghera | Sid Akbar | Eve Townsend</t>
+  </si>
+  <si>
+    <t>Drama</t>
+  </si>
+  <si>
+    <t>UK | USA</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Absinthe Film Entertainment | Focus Features | Granada Film Productions</t>
+  </si>
+  <si>
+    <t>tt4357198</t>
+  </si>
+  <si>
+    <t>L'ultime héritier</t>
+  </si>
+  <si>
+    <t>How to Make a Killing</t>
+  </si>
+  <si>
+    <t>John Patton Ford</t>
+  </si>
+  <si>
+    <t>Glen Powell | Adrian Lukis | Nell Williams | Damien Wantenaar | Sean C. Michael | Ed Harris | Grady Wilson | Maggie Toomey | Lisa Tredoux | Scarlett Van Rensburg | Ella Judes | Caellai-Joshua Hector | Emily Bruce | Alex Riley | Natasha Mayet | Natasha Nova | Nathan Roberts | Derek Griffin | Martin Munro | Margaret Qualley | James Frecheville | Raff Law | Jock Kleynhans | Aidan Scott | Jamie Nelson | Bill Camp | Mary-Anne Barlow | David Chevers | Zach Woods | Roxanne Prentice</t>
+  </si>
+  <si>
+    <t>Comedy | Drama | Thriller</t>
+  </si>
+  <si>
+    <t>UK | France</t>
+  </si>
+  <si>
+    <t>Blueprint Pictures | StudioCanal</t>
+  </si>
+  <si>
+    <t>tt31728330</t>
+  </si>
+  <si>
+    <t>They Will Kill You</t>
+  </si>
+  <si>
+    <t>Kirill Sokolov</t>
+  </si>
+  <si>
+    <t>Zazie Beetz | Patricia Arquette | Myha'la | Paterson Joseph | Tom Felton | Heather Graham | Willie Ludik | David Viviers | Gabe Gabriel | Viktoria Korotkova | James Remar | Dorothy Ann Gould | Mike Huff | Darron Meyer | Orefile Moloi | Brandon Auret | Angus Sampson | Chris van Rensburg | Neels Junior Clasen | Megan Alexander | Gert Louw | Maite Rakabe | Andrew Morgado | Robin Smith | Trudy van Rooy | Kristin Boshoff | Kylie Fisher | Hannah Gonera | Lindzay Naidoo | Shiefaa Hendricks</t>
+  </si>
+  <si>
+    <t>Action | Comedy | Horror</t>
+  </si>
+  <si>
+    <t>South Africa | USA | Canada</t>
+  </si>
+  <si>
+    <t>New Line Cinema | Nocturna | Canadian Film or Video Production Tax Credit (CPTC)</t>
+  </si>
+  <si>
+    <t>tt6930962</t>
+  </si>
+  <si>
+    <t>Walter Lapin</t>
+  </si>
+  <si>
+    <t>Spiked</t>
+  </si>
+  <si>
+    <t>Caroline Origer</t>
+  </si>
+  <si>
+    <t>Kíla Lord Cassidy | Matthew Goode | Stephen Mangan | John Hollingworth | Jeff 'Swampy' Marsh | Jules de Jongh | Charlie Reid</t>
+  </si>
+  <si>
+    <t>Animation</t>
+  </si>
+  <si>
+    <t>UK | Luxembourg | France | Belgium</t>
+  </si>
+  <si>
+    <t>French | English</t>
+  </si>
+  <si>
+    <t>Fabrique d'Images | Fantabulous | Freaks Factory</t>
+  </si>
+  <si>
+    <t>tt38649153</t>
+  </si>
+  <si>
+    <t>Assassination Classroom the Movie : Our Time</t>
+  </si>
+  <si>
+    <t>Gekijouban Ansatsu Kyoushitsu Minna no Jikan</t>
+  </si>
+  <si>
+    <t>Masaki Kitamura</t>
+  </si>
+  <si>
+    <t>Shintarô Asanuma | Mai Fuchigami | Saki Fujita | Jun Fukuyama | Kôki Harasawa | Miho Hino | Tetsu Inada | Kikuko Inoue | Shizuka Itô | Mai Kanazawa | Hisako Kanemoto | Shunsuke Kawabe | Shiho Kawaragi | Subaru Kimura | Junji Majima | Chie Matsuura | Eiji Miyashita | Daichu Mizushima | Ryô Naitô | Manami Numakura | Megumi Ogata | Nobuhiko Okamoto | Ryôta Ôsaka | Fûko Saitô | Satomi Satô | Yoshiyuki Shimozuma | Tomokazu Sugita | Ayaka Suwa | Aya Suzaki | Sayumi Suzushiro</t>
+  </si>
+  <si>
+    <t>Animation | Comedy | Sci-Fi</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>Lerche</t>
+  </si>
+  <si>
+    <t>tt13597298</t>
+  </si>
+  <si>
+    <t>Julian</t>
+  </si>
+  <si>
+    <t>Cato Kusters</t>
+  </si>
+  <si>
+    <t>Nina Meurisse | Laurence Roothooft | Rosalia Cuevas | Peter Seynaeve | Zach Hatch | Jennifer Heylen | Yannick De Coster | Joep van der Geest | David Coburn | Claire Bodson | Saskia Huybrechtse | Nanette Edens | Helena Casella | Sophie Sénécaut | Julie Capitan Fernandez | Charly Magonza | Mathilde Rault | Marie Ehouman | Sebastian Moradiellos | Ryan Sisson | Jade Wheeler | Loreanne Asratian</t>
+  </si>
+  <si>
+    <t>Belgium | Netherlands</t>
+  </si>
+  <si>
+    <t>English | French | Dutch</t>
+  </si>
+  <si>
+    <t>The Reunion | Les Films du Fleuve | Topkapi Films</t>
+  </si>
+  <si>
+    <t>tt35695538</t>
+  </si>
+  <si>
+    <t>Un jour avec mon père</t>
+  </si>
+  <si>
+    <t>My Father's Shadow</t>
+  </si>
+  <si>
+    <t>Akinola Davies</t>
+  </si>
+  <si>
+    <t>Sope Dirisu | Chibuike Marvellous Egbo | Godwin Egbo | Akerele David | Owa Orire Jeremiah | Efòn Wini | Olarotimi Fakunle | Tosin Adeyemi | Martha Ehinome | Ayo Lijadu | Patrick Diabuah | Adesina McCoy Babalola | Uzoamaka Power | Tobi Monday Solomon | Adodo Emmanuel | Yetunde Coker | Olowolaju Itunnu | Ikechukwu Gabriel | Stephen Taiwo Joseph | Patrick Essien | Andrew Ijeh | Paul Edobor | Eze Chika | Mayowa Olayinka | Abayomi Japheth | Oreofe Oguntola | Ebuka Igwe | Justice Moneke | Oluwatosin Jimoh | Micah Mavin</t>
+  </si>
+  <si>
+    <t>UK | Nigeria | Ireland</t>
+  </si>
+  <si>
+    <t>English | Yoruba</t>
+  </si>
+  <si>
+    <t>BBC Film | British Film Institute (BFI) | Crybaby Films</t>
+  </si>
+  <si>
+    <t>tt31325397</t>
+  </si>
+  <si>
+    <t>Plus forts que le diable</t>
+  </si>
+  <si>
+    <t>Graham Guit</t>
+  </si>
+  <si>
+    <t>Melvil Poupaud | Asia Argento | Marine Vacth | Raïka Hazanavicius | Nahuel Pérez Biscayart | Julie Chen | Harpo Guit | Maxi Delmelle | Chaida Chady Suku Suku | Alexandra Celestin | Heidi Johansson | Klara Vigalondo | Gladys Lefeuvre | Juliette Molina | Anjeli Pillay | Axel Perin | Youcef El Mahmoudi | Michael Zindel | Irène Benattar | Clémence Moreau</t>
+  </si>
+  <si>
+    <t>Crime | Thriller</t>
+  </si>
+  <si>
+    <t>Belgium | France</t>
+  </si>
+  <si>
+    <t>Rockstone Films | Canal+ | Ciné+OCS</t>
+  </si>
+  <si>
+    <t>tt26446095</t>
+  </si>
+  <si>
+    <t>L'odyssée de Céleste</t>
+  </si>
+  <si>
+    <t>Space Cadet</t>
+  </si>
+  <si>
+    <t>Kid Koala</t>
+  </si>
+  <si>
+    <t>Animation | Fantasy | Music</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>None | English</t>
+  </si>
+  <si>
+    <t>Films Outsiders, Les</t>
+  </si>
+  <si>
+    <t>tt17499010</t>
+  </si>
+  <si>
+    <t>Love on Trial</t>
+  </si>
+  <si>
+    <t>Renai Saiban</t>
+  </si>
+  <si>
+    <t>Kôji Fukada</t>
+  </si>
+  <si>
+    <t>Kyoko Saito | Yuki Kura | Erika Karata | Kenjiro Tsuda | Atsushi Hashimoto</t>
+  </si>
+  <si>
+    <t>Toho | Knockonwood</t>
+  </si>
+  <si>
+    <t>tt11611166</t>
+  </si>
+  <si>
+    <t>L'île de la demoiselle</t>
+  </si>
+  <si>
+    <t>L'île de la Demoiselle</t>
+  </si>
+  <si>
+    <t>Micha Wald</t>
+  </si>
+  <si>
+    <t>Alexandra Lamy | Salomé Dewaels | Alexandre Gavras | Patrick Descamps | Louis Peres | Candice Bouchet | Corentin Lobet | Sébastien Dupont-Bloch | Eddy Frogeais</t>
+  </si>
+  <si>
+    <t>Stenola Productions | K.G. Productions | Czar Film</t>
+  </si>
+  <si>
+    <t>tt35889287</t>
+  </si>
+  <si>
+    <t>Les Filles du ciel</t>
+  </si>
+  <si>
+    <t>Les filles du ciel</t>
+  </si>
+  <si>
+    <t>Bérangère McNeese</t>
+  </si>
+  <si>
+    <t>Héloïse Volle | Shirel Nataf | Yowa-Angélys Tshikaya | Mona Berard | Alba d'Abbundo | Olympe d'Abbundo | Jonas Bloquet | Bilel Chegrani | Hugo Dillon | Tarik Lebal | Kamel Laadaili | Jeremy Lewin | Youssef Mys | Cyril Gueï | Anne Coesens | Thomas Bergès | Valentin Marro | Guillermo Guiz | Antoine Godson | Antoine Suarez-Pazos | Mathieu Beaufromé | Mehdi Léger | Pierre Cartonnet | David Berthier | Dominic Gould | Adriana Da Fonseca | Léna Cayrade | Rémy Gence | Bertrand De Ruyver | Laurence Flahault</t>
+  </si>
+  <si>
+    <t>France | Belgium</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>Paprika Films | Kwassa Films | Pictanovo</t>
+  </si>
+  <si>
+    <t>tt26733325</t>
+  </si>
+  <si>
+    <t>Une jeunesse indienne</t>
+  </si>
+  <si>
+    <t>Homebound</t>
+  </si>
+  <si>
+    <t>Neeraj Ghaywan</t>
+  </si>
+  <si>
+    <t>Ishaan Khatter | Vishal Jethwa | Janhvi Kapoor | Harshika Parmar | Dadhi R Paandey | Shalini Vatsa | Chandan K. Anand | Pankaj Dubey | Sudipta Saxena | Shreedhar Dubey | Kuldeep Raghuvanshi | Yogendra Vikram Singh | Preet Kumar | Abu Suffiyan | Arpit Mishra | Raghav Gite | Tejas Mathur | Aarti Kale | Rajendra Parsaniya | Jaya Rajeshwar | Shivanshu Singh | Zakir Baig | Aadil Shakeel | Ramkrishan Dhakar | Akanksha Ojha | Vijay Vikram Singh | Dayasagar Dharua | Fatima Sheikh | Parvez Sayyed | Sanjot Patil</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Hindi</t>
+  </si>
+  <si>
+    <t>Dharma Productions | Toscan du Plantier</t>
+  </si>
+  <si>
+    <t>tt32244884</t>
+  </si>
+  <si>
+    <t>La couleuvre noire</t>
+  </si>
+  <si>
+    <t>Aurélien Vernhes-Lermusiaux</t>
+  </si>
+  <si>
+    <t>Alexis Tafur | Miguel Angel Viera | Angela Rodriguez | Laura Valentina Quintero | Virgelina Gil Saénz | Santiago Porras | Laura Rodríguez | Jonathan Mortensen | Bartek Brzozowski | Joseph Fuzessy | Martha Inés Mazo Loaiza | Oscar Bajoreno | Andrés Cardozo | Michal Steven | Jhon Jaime Bustos | Nery Tovar Vanegas | Stefanny Marquez</t>
+  </si>
+  <si>
+    <t>France | Brazil | Colombia</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>Dublin Films | Burning | Vulcana Cinema</t>
+  </si>
+  <si>
+    <t>tt34812090</t>
+  </si>
+  <si>
+    <t>Lupin the IIIrd the Movie: la lignée immortelle</t>
+  </si>
+  <si>
+    <t>Rupan Sansei za Mûbî Fujimi no Ketsuzoku</t>
+  </si>
+  <si>
+    <t>Takeshi Koike</t>
+  </si>
+  <si>
+    <t>Kan'ichi Kurita | Abril Bellido | Richard Epcar | Lexi Fontaine | Takaya Hashi | Akio Hirose | Kelsey Jaffer | Mizukawa Katamari | Ainosuke Kataoka | Miyuki Kobori | Lex Lang | Blythe Melin | Aoi Morikawa | Daisuke Namikawa | Kanji Obana | Michael Orenstein | Sayaka Osawa | Akio Ôtsuka | Miyuki Sawashiro | Sumi Shimamoto | Keith Silverstein | Mogura Suzuki | Minami Takayama | Cristina Valenzuela | Dan Woren | Kôichi Yamadera</t>
+  </si>
+  <si>
+    <t>Animation | Action | Adventure</t>
+  </si>
+  <si>
+    <t>Chûôkôron Shinsha | Futabasha | TMS Entertainment</t>
+  </si>
+  <si>
+    <t>tt21257788</t>
+  </si>
+  <si>
+    <t>Les saisons</t>
+  </si>
+  <si>
+    <t>As estações</t>
+  </si>
+  <si>
+    <t>Maureen Fazendeiro</t>
+  </si>
+  <si>
+    <t>Simão Ramalho | Cláudio da Silva | Ana Potra | Manuel Leitão | António Sozinho | Gerti Drassl | Michaela Kaspar | Raphael von Bargen | Toni Slama | António Abel | Simão Romeu</t>
+  </si>
+  <si>
+    <t>Documentary</t>
+  </si>
+  <si>
+    <t>Portugal | France | Spain | Austria</t>
+  </si>
+  <si>
+    <t>Portuguese | German</t>
+  </si>
+  <si>
+    <t>Filmika Galaika | Nabis Filmgroup | Norte Productions</t>
+  </si>
+  <si>
+    <t>tt32279108</t>
+  </si>
+  <si>
+    <t>Derrière les drapeaux, le soleil</t>
+  </si>
+  <si>
+    <t>Bajo las banderas, el sol</t>
+  </si>
+  <si>
+    <t>Juanjo Pereira</t>
+  </si>
+  <si>
+    <t>Alfredo Stroessner | Lyndon B. Johnson | Georges Pompidou | Andrés Rodríguez | Jorge Rafael Videla</t>
+  </si>
+  <si>
+    <t>Paraguay | Argentina | Germany | USA | France</t>
+  </si>
+  <si>
+    <t>Guarani | Spanish | German | French | English | Portuguese</t>
+  </si>
+  <si>
+    <t>Cine Mío | Bird Street Productions | Lardux Films</t>
+  </si>
+  <si>
+    <t>tt15574270</t>
+  </si>
+  <si>
+    <t>I saw the TV glow</t>
+  </si>
+  <si>
+    <t>I Saw the TV Glow</t>
+  </si>
+  <si>
+    <t>Jane Schoenbrun</t>
+  </si>
+  <si>
+    <t>Justice Smith | Jack Haven | Ian Foreman | Helena Howard | Lindsey Jordan | Danielle Deadwyler | Fred Durst | Conner O'Malley | Emma Portner | Madaline Riley | Amber Benson | Albert Birney | Michael C. Maronna | Danny Tamberelli | Tim Griffin Allan | Tyler Dean Flores | Elizabeth Scopel | Marlyn Bandiero | Haley Dahl | Raina Block | Bailey Wollowitz | Lily Reszi Rothman | Phoebe Bridgers | Kris Esfandiari | Wilson Flores | Thommy Northcut | Julie Lodhy</t>
+  </si>
+  <si>
+    <t>Drama | Horror | Mystery</t>
+  </si>
+  <si>
+    <t>USA | UK</t>
+  </si>
+  <si>
+    <t>A24 | Fruit Tree | Smudge Films</t>
+  </si>
+  <si>
+    <t>tt15940132</t>
+  </si>
+  <si>
+    <t>War Machine</t>
+  </si>
+  <si>
+    <t>Patrick Hughes</t>
+  </si>
+  <si>
+    <t>Alan Ritchson | Stephan James | Blake Richardson | Dennis Quaid | Esai Morales | Jai Courtney | Alex King | Keiynan Lonsdale | Jack Patten | James Beaufort | Joshua Diaz | Jacob Hohua | Daniel Webber | Richard Cotta | Matt Testro | Victory Ndukwe | Heather Burridge | Justin Wang | Elias Anton | Jake Ryan | Christopher Kirby | Joey Vieira | Ditch Davey | Ronald Medcraft | Bilal Younus | Joseph Bruce | Craig Johnston | Greg Kleynjans | Patrick Hughes | Sean Lally</t>
+  </si>
+  <si>
+    <t>Action | Sci-Fi | Thriller</t>
+  </si>
+  <si>
+    <t>UK | Australia | New Zealand | USA</t>
+  </si>
+  <si>
+    <t>Emu Creek Pictures | Hidden Pictures | Huge Films</t>
+  </si>
+  <si>
+    <t>tt33071426</t>
+  </si>
+  <si>
+    <t>The Drama</t>
+  </si>
+  <si>
+    <t>Kristoffer Borgli</t>
+  </si>
+  <si>
+    <t>Zendaya | Robert Pattinson | Alana Haim | Mamoudou Athie | Hailey Gates | Sydney Lemmon | Hannah Gross | Anna Baryshnikov | Jordyn Curet | Michael Abbott Jr. | Zoë Winters | Dee Nelson | Damon Gupton | Ken Cheeseman | Doria Bramante | Jordan Raf | Jeremy Levick | Sam Zimman | Celia Rowlson-Hall | Greer Cohen | Shawn Fogarty | Michele Proude | Kelly Butler</t>
   </si>
   <si>
     <t>Comedy | Drama | Romance</t>
   </si>
   <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Tamil</t>
-  </si>
-  <si>
-    <t>MRP Entertainment | Soundarya Rajinikanth's Zion Films</t>
-  </si>
-  <si>
-    <t>tt37537155</t>
-  </si>
-  <si>
-    <t>Ashakal Aayiram</t>
-  </si>
-  <si>
-    <t>G. Prajith</t>
-  </si>
-  <si>
-    <t>Jayaram | Kalidas Jayaram | Ishaani Krishna | Anand Manmadhan | Dileep Menon | Akhil Nrd | Ramesh Pisharody | Zhinz Shan | Sharafudheen | Asha Sharath</t>
-  </si>
-  <si>
-    <t>Family</t>
-  </si>
-  <si>
-    <t>Malayalam</t>
-  </si>
-  <si>
-    <t>Sree Gokulam Movies</t>
-  </si>
-  <si>
-    <t>tt39216314</t>
-  </si>
-  <si>
-    <t>Stray Kids: The dominATE Experience</t>
-  </si>
-  <si>
-    <t>Paul Dugdale | Farah Khalid</t>
-  </si>
-  <si>
-    <t>Bang Chan | Lee Know | Seo Changbin | Hwang Hyun-jin | Han Jisung | Felix Lee | Kim Seungmin | Yang Jeong-in | Stray Kids</t>
-  </si>
-  <si>
-    <t>Documentary | Music</t>
-  </si>
-  <si>
     <t>USA</t>
   </si>
   <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Live Nation Studios</t>
-  </si>
-  <si>
-    <t>tt27722575</t>
-  </si>
-  <si>
-    <t>200 % Loup</t>
-  </si>
-  <si>
-    <t>200% Wolf</t>
-  </si>
-  <si>
-    <t>Alexs Stadermann</t>
-  </si>
-  <si>
-    <t>Ilai Swindells | Elizabeth Nabben | Jennifer Saunders | Sarah Georgina | Peter McAllum | Samara Weaving | Janice Petersen | Heather Mitchell | Michael Bourchier | Alexs Stadermann | Akmal Saleh | Sarah Harper | Anna Nguyen | Shirley Yao | Matias Biondi | Eden Diebel | Agatha Ozdowska | Tracy Lenon | Jonathan Tappin | Caz Prescott | Virginie Laverdure | Ant Simpson</t>
-  </si>
-  <si>
-    <t>Animation | Action | Adventure</t>
-  </si>
-  <si>
-    <t>Australia | Germany | Spain | Mexico</t>
-  </si>
-  <si>
-    <t>Flying Bark Productions | Atlántika Films | 200 Wolf La Pelicula AIE</t>
-  </si>
-  <si>
-    <t>tt35659725</t>
-  </si>
-  <si>
-    <t>Les Légendaires, le film</t>
-  </si>
-  <si>
-    <t>Les Légendaires</t>
-  </si>
-  <si>
-    <t>Guillaume Ivernel</t>
-  </si>
-  <si>
-    <t>Roman Doduik | Esthèle Dumand | Thomas Sagols | Antoine Schoumsky | Élise Tilloloy | Damien Witecka | Arthur Raynal | Lila Lacombe | Marjorie Frantz | Lucien Jean-Baptiste | Aurélie Konaté | Christophe Lemoine | Bernard Lanneau | Dorothée Pousséo | Penny Padilla | Nathanaël Perrot | Mila Pointet | Isaac Schoumsky | Kendell Byrd | Paul Castro Jr. | Etienne Moana</t>
+    <t>A24 | Live Free or Die Films | Square Peg</t>
+  </si>
+  <si>
+    <t>tt28650488</t>
+  </si>
+  <si>
+    <t>Super Mario Galaxy, le film</t>
+  </si>
+  <si>
+    <t>The Super Mario Galaxy Movie</t>
+  </si>
+  <si>
+    <t>Aaron Horvath | Michael Jelenic | Pierre Leduc | Fabien Polack</t>
+  </si>
+  <si>
+    <t>Brie Larson | Virginia Dare Jelenic | Benny Safdie | Kevin Michael Richardson | Chris Pratt | Charlie Day | Donald Glover | Keegan-Michael Key | Anya Taylor-Joy | Eric Bauza | Jack Black | Roxana Ortega | Luis Guzmán | Issa Rae | Ed Skudder | Glen Powell | Juliet Jelenic | Carlos Alazraqui | Hope Levy | Monia Ayachi | Ashley London | Ryan Bartley | Eric Lopez | Rachel Butera | Scott Menville | Jessica DiCicco | Laraine Newman | Johnny Gidcomb | Matt Nolan | Danielle Hartnett</t>
+  </si>
+  <si>
+    <t>Animation | Adventure | Comedy</t>
+  </si>
+  <si>
+    <t>Japan | USA</t>
+  </si>
+  <si>
+    <t>Universal Pictures | Nintendo | Illumination Entertainment</t>
+  </si>
+  <si>
+    <t>tt39814688</t>
+  </si>
+  <si>
+    <t>Compostelle</t>
+  </si>
+  <si>
+    <t>Yann Samuell</t>
+  </si>
+  <si>
+    <t>Alexandra Lamy | Julien Le Berre | Maëlle Vidou | Eric Métayer | Malik Amraoui | Mélanie Doutey | Cyril Gueï | James Joint | Bruno Such</t>
+  </si>
+  <si>
+    <t>Eveya Productions | Page Films | Apollo Films</t>
+  </si>
+  <si>
+    <t>tt31514146</t>
+  </si>
+  <si>
+    <t>Plus fort que moi</t>
+  </si>
+  <si>
+    <t>I Swear</t>
+  </si>
+  <si>
+    <t>Kirk Jones</t>
+  </si>
+  <si>
+    <t>Robert Aramayo | Maxine Peake | Somerled Campbell | Michael Dylan | David Carlyle | Christina Ashford | Scott Ellis Watson | Sanjeev Kohli | Steven Cree | Ethan Stewart | Isla Mercer | Catriona McArthur | Shirley Henderson | Paul Donnelly | Ron Donachie | Jamie McAllister | Abigail Noon | Ella Victoria Robb | Sam Felderhof | Isaac Chan Adams | Leah MacRae | Taqi Nazeer | Liam Campbell | Douglas Rankine | Francesco Piacentini-Smith | Anna-Jorge Somerville | Connor Parkin | Holly Howden Gilchrist | Calum Cormack | Amber Sylvia Edwards</t>
+  </si>
+  <si>
+    <t>Biography | Drama</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>One Story High | Tempo Productions | StudioCanal Films</t>
+  </si>
+  <si>
+    <t>tt39314864</t>
+  </si>
+  <si>
+    <t>Mauvaise pioche</t>
+  </si>
+  <si>
+    <t>Gérard Jugnot</t>
+  </si>
+  <si>
+    <t>Gérard Jugnot | Philippe Lacheau | Thierry Lhermitte | Zabou Breitman | Jean-Pierre Darroussin | Michèle Laroque | Reem Kherici | François Morel | Charlotte Gabris | Claudia Bacos | François Bureloup | Philippe Duquesne | Josiane Balasko | Clément Bonnier | Stéphane Chollet | Iñaki Lartigue | Lionel Rosso | Julien Simon</t>
+  </si>
+  <si>
+    <t>Comedy</t>
   </si>
   <si>
     <t>France</t>
   </si>
   <si>
-    <t>French</t>
-  </si>
-  <si>
-    <t>Pan Européenne | Pan Cinema | Belvision</t>
-  </si>
-  <si>
-    <t>tt30959077</t>
-  </si>
-  <si>
-    <t>Le grand Phuket</t>
-  </si>
-  <si>
-    <t>Xiao Ban Jie</t>
-  </si>
-  <si>
-    <t>Yaonan Liu</t>
-  </si>
-  <si>
-    <t>You Junfen | Hang Kang | Li Rongkun | Xuan Yang | Liu Hui Yuan</t>
-  </si>
-  <si>
-    <t>Drama</t>
-  </si>
-  <si>
-    <t>Hong Kong | France | Belgium | Germany</t>
-  </si>
-  <si>
-    <t>Mandarin</t>
-  </si>
-  <si>
-    <t>A Private View | Remora Films | Wood Water Films</t>
-  </si>
-  <si>
-    <t>tt35890599</t>
-  </si>
-  <si>
-    <t>N121 - Bus de nuit</t>
-  </si>
-  <si>
-    <t>Morade Aissaoui</t>
-  </si>
-  <si>
-    <t>Riadh Belaïche | Bakary Diombera | Gaspard Gevin-Hié | Paola Locatelli | Aïssatou Diallo Sagna | Arben Bajraktaraj | Mylène Jampanoï | Lucie Charles-Alfred | Laurence Oltuski | Jérémie Covillault | Damien Jouillerot | Azad Boutella | Bounsy Luang Phinith | Beidja Yahiaoui | Audrey Marnay | Louis Duneton | Lahcen Kourkdane | Camille Verschuère | Mauricette Gourdon | Niddal El Mellouhi | Amine Boughanem | Thibault Dyevre | Wissam Toubal | Sofia Ghoul | Abel Mansouri Asselain | Jawad Outoui | Sami Amara | Noémie Desbordes</t>
-  </si>
-  <si>
-    <t>France | Belgium</t>
-  </si>
-  <si>
-    <t>No Info</t>
-  </si>
-  <si>
-    <t>Ripley Films | Cheyenne Federation | Wild Bunch Distribution</t>
-  </si>
-  <si>
-    <t>tt36580119</t>
-  </si>
-  <si>
-    <t>Le gâteau du président</t>
-  </si>
-  <si>
-    <t>Mamlaket al-qasab</t>
-  </si>
-  <si>
-    <t>Hasan Hadi</t>
-  </si>
-  <si>
-    <t>Baneen Ahmad Nayyef | Waheed Thabet Khreibat | Sajad Mohamad Qasem | Muthanna Malaghi | Ahmad Qasem Saywan | Maytham Mreidi | Rahim AlHaj | Thaer Salem | Ali Khalaf | Fatima Abouharoon | Mahmoud Mazen Lazen | Aqeel Wadi | Mohammed Rheimeh | Rokia Alwadi | Ali Saddam Najem | Abdelkarim Jasim | Mohammad Qasem | Raed Harbi Abdeljalil | Elaf Mohamed | Ahmed Al-Hayali | Mohammed Zaid | Al-Hassan Adnan | Mohammed Ammar | Ahmad Hameed Ahmad | Haidar Jamal Jaber | Aqeel Al Shamri | Tayseer Ibrahim Radi | Nadia Rashak</t>
-  </si>
-  <si>
-    <t>Iraq | Qatar | USA</t>
-  </si>
-  <si>
-    <t>Arabic</t>
-  </si>
-  <si>
-    <t>Maiden Voyage Pictures | Missing Piece Films | Spark Features</t>
-  </si>
-  <si>
-    <t>tt31050594</t>
-  </si>
-  <si>
-    <t>Reconnu Coupable</t>
-  </si>
-  <si>
-    <t>Mercy</t>
-  </si>
-  <si>
-    <t>Timur Bekmambetov</t>
-  </si>
-  <si>
-    <t>Chris Pratt | Rebecca Ferguson | Kali Reis | Annabelle Wallis | Chris Sullivan | Kylie Rogers | Jeff Pierre | Rafi Gavron | Kenneth Choi | Jamie McBride | Ross Gosla | Mark Daneri | Haydn Dalton | Michael C. Mahon | Noah Fearnley | Konstantin Podprugin | Cully Pratt | Philicia Saunders | Jay Jackson | Mahmoud Mahmoud | Anja Akstin | Katario Dupreè Young | Evgenia Sinitsin | Richard Cetrone | Renata Ribeiro | Mike Tarnofsky | John Bubniak | Tom Rezvan | Kory Ison | Veronica Rose</t>
-  </si>
-  <si>
-    <t>Action | Crime | Drama</t>
-  </si>
-  <si>
-    <t>Russia | USA</t>
-  </si>
-  <si>
-    <t>Amazon MGM Studios | Atlas Entertainment | Bazelevs Entertainment</t>
-  </si>
-  <si>
-    <t>tt28865633</t>
-  </si>
-  <si>
-    <t>La lumière ne meurt jamais</t>
-  </si>
-  <si>
-    <t>Jossain on valo joka ei sammu</t>
-  </si>
-  <si>
-    <t>Lauri-Matti Parppei</t>
-  </si>
-  <si>
-    <t>Samuel Kujala | Anna Rosaliina Kauno | Camille Auer | Kaisa-Leena Koskenkorva | Mari Rantasila | Jarkko Pajunen | Matti Mustonen</t>
-  </si>
-  <si>
-    <t>Comedy | Drama</t>
-  </si>
-  <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>Finnish | English | French</t>
-  </si>
-  <si>
-    <t>Goodtime Pictures | Made</t>
-  </si>
-  <si>
-    <t>tt31557492</t>
-  </si>
-  <si>
-    <t>Les âmes bossales</t>
-  </si>
-  <si>
-    <t>Francois Perlier</t>
-  </si>
-  <si>
-    <t>Documentary</t>
-  </si>
-  <si>
-    <t>Haiti | France</t>
-  </si>
-  <si>
-    <t>French | Haitian</t>
-  </si>
-  <si>
-    <t>Corpus Films</t>
-  </si>
-  <si>
-    <t>tt33455099</t>
-  </si>
-  <si>
-    <t>The Mastermind</t>
-  </si>
-  <si>
-    <t>Kelly Reichardt</t>
-  </si>
-  <si>
-    <t>Josh O'Connor | Sterling Thompson | Alana Haim | Jasper Thompson | Bill Camp | Hope Davis | Eli Gelb | Cole Doman | Carrie Lazar | Javion Allen | Reighan Bean | Katie Hubbard | Margot Anderson-Song | Avery Deutsch | Deb G. Girdler | Richard Hagerman | Juan Carlos Hernández | Ryan Homchick | Matthew Maher | Marc Ross | Rick Dutrow | Clark Harris | John Magaro | Gaby Hoffmann | Kevin Michael Walsh | Amanda Plummer | Mauricio Soliz | Rhenzy Feliz | Kade Clarks | Mark Antony Howard</t>
-  </si>
-  <si>
-    <t>Crime</t>
-  </si>
-  <si>
-    <t>USA | UK</t>
-  </si>
-  <si>
-    <t>English | French</t>
-  </si>
-  <si>
-    <t>Film Science | MUBI</t>
-  </si>
-  <si>
-    <t>tt29567915</t>
-  </si>
-  <si>
-    <t>Nuremberg</t>
-  </si>
-  <si>
-    <t>James Vanderbilt</t>
-  </si>
-  <si>
-    <t>Rami Malek | Russell Crowe | Michael Shannon | Leo Woodall | John Slattery | Richard E. Grant | Mark O'Brien | Colin Hanks | Wrenn Schmidt | Andreas Pietschmann | Lydia Peckham | Lotte Verbeek | Dieter Riesle | Peter Jordan | Tom Keune | Fleur Bremmer | Ben Miles | Giuseppe Cederna | Paul Antony-Barber | Michael Sheldon | Donald Sage Mackay | Sam Newman | Jeremy Wheeler | Wayne Brett | Blake Kubena | Jonty Peach | Carl Achleitner | Christian Löber | Laurence Pears | Billy Rayner</t>
+    <t>M.E.S. Productions | TF1 Films Production | Malec Productions</t>
+  </si>
+  <si>
+    <t>tt32888226</t>
+  </si>
+  <si>
+    <t>Yellow Letters</t>
+  </si>
+  <si>
+    <t>Gelbe Briefe</t>
+  </si>
+  <si>
+    <t>Ilker Çatak</t>
+  </si>
+  <si>
+    <t>Yusuf Akgün | Emre Bakar | Tansu Biçer | Ipek Bilgin | Leyla Smyrna Cabas | Kerem Can | Aziz Çapkurt | Siir Eloglu | Ömer Filikci | Elit Iscan | Özgü Namal | Ipek Seyalioglu | Yusuf Özhan Tali | Uygar Tamer | Sultan Ulutas | Eray von Egilmez | Aycil Yeltan</t>
+  </si>
+  <si>
+    <t>Germany | France | Turkey</t>
+  </si>
+  <si>
+    <t>Turkish</t>
+  </si>
+  <si>
+    <t>if... Productions | Haut et Court | Liman Film</t>
+  </si>
+  <si>
+    <t>tt27811632</t>
+  </si>
+  <si>
+    <t>Silent Friend</t>
+  </si>
+  <si>
+    <t>Stille Freundin</t>
+  </si>
+  <si>
+    <t>Ildikó Enyedi</t>
+  </si>
+  <si>
+    <t>Tony Leung Chiu-wai | Luna Wedler | Enzo Brumm | Léa Seydoux | Sylvester Groth | Yun Huang | Luca Valentini | Felix Burose | Rainer Bock | Marlene Burow | Erwin Giese | Johannes Hegemann | Sky Hofmann | Johannes Scheidweiler | Martin Wuttke</t>
   </si>
   <si>
     <t>Biography | Drama | History</t>
   </si>
   <si>
-    <t>USA | Hungary</t>
-  </si>
-  <si>
-    <t>English | German</t>
-  </si>
-  <si>
-    <t>Walden Media | Filmsquad | Mythology Entertainment</t>
-  </si>
-  <si>
-    <t>tt36599377</t>
-  </si>
-  <si>
-    <t>La vie après Siham</t>
-  </si>
-  <si>
-    <t>Namir Abdel Messeeh</t>
-  </si>
-  <si>
-    <t>Waguih Abdel Messeeh | Namir Abdel Messeeh</t>
-  </si>
-  <si>
-    <t>France | Egypt</t>
-  </si>
-  <si>
-    <t>Oweda Films | Les Films d'Ici | Ambient Light</t>
-  </si>
-  <si>
-    <t>tt33029380</t>
-  </si>
-  <si>
-    <t>Marsupilami</t>
-  </si>
-  <si>
-    <t>Philippe Lacheau</t>
-  </si>
-  <si>
-    <t>Philippe Lacheau | Jamel Debbouze | Tarek Boudali | Élodie Fontan | Julien Arruti | Alban Ivanov | Corentin Guillot | Reem Kherici | Jean Reno | Gérard Jugnot | Didier Bourdon | Paco Boisson | Jamel Elgharbi | Catherine Giron | Kamel Laadaili | Adeline Tayoro | Alexandros Giannou | Youssef Sahraoui | Arthur Sanigou | Hassen Boubritou | Laurent Spielvogel | Jean-Philippe Paravisini | Enlil Albanna | Alexis Boucot | Vincent Desagnat | Nathalie Kent | Cédric Rigaut | Booder | Romain Lancry | David Faure</t>
-  </si>
-  <si>
-    <t>Adventure | Comedy | Family</t>
-  </si>
-  <si>
-    <t>Pathé | Baf Prod | TF1 Films Production</t>
-  </si>
-  <si>
-    <t>tt31777964</t>
-  </si>
-  <si>
-    <t>Gourou</t>
-  </si>
-  <si>
-    <t>Yann Gozlan</t>
-  </si>
-  <si>
-    <t>Pierre Niney | Marion Barbeau | Anthony Bajon | Christophe Montenez | Jonathan Turnbull | Raphaëlle Simon | Tracy Gotoas | Holt McCallany | Léonie Simaga | Manon Kneusé | Paul Scarfoglio | Deborah Grall | Leanna Chea | Mazigh Bouaich | Eric Khanthavixay | Sonia Imbert | César Méric | Céline Carrère | Éric Naggar | Elric Covarel Garcia | Alexandre Malesson | Alex Elliott | Laurie Catherine Winkel | Charlotte Houdin | Youri Lauriette | Zoé Garcia | Costa Canda | Abdallah Charki | Lenni Prezelin | Paco Fuster</t>
+    <t>Germany | Hungary | France | China</t>
+  </si>
+  <si>
+    <t>English | German | Cantonese</t>
+  </si>
+  <si>
+    <t>Pandora Filmproduktion | Inforg-M&amp;M Film Kft. | Galatée Films</t>
+  </si>
+  <si>
+    <t>tt23644354</t>
+  </si>
+  <si>
+    <t>Derrière les palmiers</t>
+  </si>
+  <si>
+    <t>Meryem Benm'Barek</t>
+  </si>
+  <si>
+    <t>Sara Giraudeau | Driss Ramdi | Nadia Kounda | Carole Bouquet | Olivier Rabourdin | Soumaya Akaaboune | Amine Ennaji | Ayoub Trombati | Fatima Herandi Raouya | Rachel O'Meara | Houda Baghdad | Abdellah Jued | Steve Canillac | Salma Machkour | Sonia Okacha | Brice Bexter | Ahlam Marouane | Sanae Regragui | Zakaria Meskabi | Abdellah Lebkiri | Nazim Aboudaoud</t>
   </si>
   <si>
     <t>Thriller</t>
   </si>
   <si>
-    <t>Wy Productions | Ninety Films | StudioCanal</t>
-  </si>
-  <si>
-    <t>tt29612071</t>
-  </si>
-  <si>
-    <t>Biscuit le chien fantastique</t>
-  </si>
-  <si>
-    <t>Charlie the Wonderdog</t>
-  </si>
-  <si>
-    <t>Shea Wageman</t>
-  </si>
-  <si>
-    <t>Owen Wilson | Tabitha St. Germain | Sebastian Billingsley-Rodriguez | Rhona Rees | Caitlynne Medrek | Ruairi MacDonald | Anthony Bolognese | Emily Delahunty | David Dixon | Jenn Rogan | Mela Pietropaolo | Lindsay Gibson | Dawson Littman | Zac Bennett-McPhee</t>
-  </si>
-  <si>
-    <t>Animation | Comedy | Family</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>ICON Creative Studio | Centurion Pictures</t>
-  </si>
-  <si>
-    <t>tt33311007</t>
-  </si>
-  <si>
-    <t>Promis le ciel</t>
-  </si>
-  <si>
-    <t>Erige Sehiri</t>
-  </si>
-  <si>
-    <t>Aïssa Maïga | Laetitia Ky | Debora Lobe Naney | Mohamed Grayaâ | Foued Zaazaa | Estelle Kenza Dpgbo | Touré Blamassi | Roxanne Takouri | Marie-Noël Ngwe | Elisabeth Kongolo Badibanga | Zohe Malunda | Elly Franck Biboum | David Emmanuel Biboum | Yate Amos Bebo | Viviane Boudouaahou | Kouakou William Konan | Yao Koff Siméon | Charlotte Ourega | Flora Bozoua | Jean Claude Yué | Christ Jordan</t>
-  </si>
-  <si>
-    <t>Tunisia | France | Qatar</t>
-  </si>
-  <si>
-    <t>Arabic | French</t>
-  </si>
-  <si>
-    <t>Maneki Films | Henia Production | Canal+</t>
-  </si>
-  <si>
-    <t>tt33616511</t>
-  </si>
-  <si>
-    <t>Bel Ami</t>
-  </si>
-  <si>
-    <t>Piao liang peng you</t>
-  </si>
-  <si>
-    <t>Jun Geng</t>
-  </si>
-  <si>
-    <t>Xuanyu Chen | Qing Wang | Zixing Wang | Gang Xu | Baohe Xue | Liguo Yuan | Zhiyong Zhang</t>
-  </si>
-  <si>
-    <t>France | China</t>
-  </si>
-  <si>
-    <t>Chinese | English</t>
-  </si>
-  <si>
-    <t>Blackfin Production</t>
-  </si>
-  <si>
-    <t>tt34886821</t>
-  </si>
-  <si>
-    <t>La grazia</t>
-  </si>
-  <si>
-    <t>Paolo Sorrentino</t>
-  </si>
-  <si>
-    <t>Toni Servillo | Anna Ferzetti | Orlando Cinque | Massimo Venturiello | Milvia Marigliano | Giuseppe Gaiani | Giovanna Guida | Alessia Giuliani | Roberto Zibetti | Vasco Mirandola | Linda Messerklinger | Rufin Doh Zeyenouin | Simone Colombari | Alexandra Gottschlich | Lucio Zagaria | Francesco Martino | Tommaso Amadio | Guè Pequeno | Shablo | Fabrizio Bordignon | Alessandro Salvatori | Michele Azzarito | Elisa Perolini | Giorgia Liguori | Cesare Scova | Giulio Prosperi | Ernesto Caccetta | Alessia Santini | Stefania Barca | Federica Corti</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>Italian</t>
-  </si>
-  <si>
-    <t>The Apartment | Numero 10 | PiperFilm</t>
-  </si>
-  <si>
-    <t>tt32558601</t>
-  </si>
-  <si>
-    <t>Baise-en-ville</t>
-  </si>
-  <si>
-    <t>Martin Jauvat</t>
-  </si>
-  <si>
-    <t>Martin Jauvat | Emmanuelle Bercot | William Lebghil | Sébastien Chassagne | Anaïde Rozam | Michel Hazanavicius | Mahaut Adam | Annabelle Lengronne | Eva Huault | Aurélien Bellanger | Géraldine Pailhas | Georges Pillegand | Louise Blachère | Erwin Aureillan | Jean-Luc Vincent | Ferdinand Niquet-Rioux | Mike Bujoli | Marlon Macias | Mélanie Bourgeois | Mahamadou Sangaré | Nicolas Delys | Inès Dumont | Akira Seto-Chaumet</t>
-  </si>
-  <si>
-    <t>Comedy</t>
-  </si>
-  <si>
-    <t>Ecce Films | France 2 Cinéma | Netflix</t>
-  </si>
-  <si>
-    <t>tt35932382</t>
-  </si>
-  <si>
-    <t>À demain sur la lune</t>
-  </si>
-  <si>
-    <t>Thomas Balmès</t>
-  </si>
-  <si>
-    <t>Hassen Bouchakour</t>
-  </si>
-  <si>
-    <t>TBC Productions</t>
-  </si>
-  <si>
-    <t>tt22868010</t>
-  </si>
-  <si>
-    <t>Retour à Silent Hill</t>
-  </si>
-  <si>
-    <t>Return to Silent Hill</t>
-  </si>
-  <si>
-    <t>Christophe Gans</t>
-  </si>
-  <si>
-    <t>Jeremy Irvine | Hannah Emily Anderson | Robert Strange | Ljiljana Velimirov | Giulia Pelagatti | Evie Templeton | Pearse Egan | Eve Macklin | Emily Carding | Nicola Alexis | Martine Richards | Howard Saddler | Matteo Pasquini | Melissa Graham | Lara Duru | Karya Duru | Alana Maria | Rhiannon Moushall | Slavisa Ivanovic | Adam Basil | Masa Anic | Ljudmila Korobova | Ana Obradovic | Anastasija Kanazarevic | Marija Milicevic | Tamara Ristoska | Jasper Salon | Sandy E. Scott</t>
-  </si>
-  <si>
-    <t>Drama | Horror | Mystery</t>
-  </si>
-  <si>
-    <t>France | USA | UK | Germany | Serbia | Japan</t>
-  </si>
-  <si>
-    <t>Davis Films | The Electric Shadow Company | Supernix</t>
-  </si>
-  <si>
-    <t>tt37660587</t>
-  </si>
-  <si>
-    <t>À pied d'œuvre</t>
-  </si>
-  <si>
-    <t>À pied d'oeuvre</t>
-  </si>
-  <si>
-    <t>Valérie Donzelli</t>
-  </si>
-  <si>
-    <t>Adrien Barazzone | Valérie Donzelli | Claude Perron | Béatrice de Staël | Mamadou Diallo | Thelma Pourias | Oscar Tillette | Eve Oron | Marion Lecrivain | Benoît Carre | Ahlam Slama | Hélène Rimenaid | Clémence Coullon | Carmen Kouyaté | Pauline Serieys | Sacha Wintz | Rei Watanabe | Maly Diallo | Michel Gondry | Pauline Fugaldi | Éric Reinhardt | Marie Aubrun | Christopher Thompson | Naëlle Dariya | Jérémie Laure | Marion Jadot | Benjamin Clery | Franc Bruneau | Isabelle Goev | Soufiane Sarr</t>
-  </si>
-  <si>
-    <t>Biography | Drama</t>
-  </si>
-  <si>
-    <t>Pitchipoï Productions | France 2 Cinéma | Canal+</t>
-  </si>
-  <si>
-    <t>tt32263650</t>
-  </si>
-  <si>
-    <t>Christy and His Brother</t>
-  </si>
-  <si>
-    <t>Christy</t>
-  </si>
-  <si>
-    <t>Brendan Canty</t>
-  </si>
-  <si>
-    <t>Danny Power | Diarmuid Noyes | AJ Brown | Arla Brown | Emma Willis | Darren Stewart | Jamie Forde | Cara Cullen | Sophie McNamara | Ciaran Bermingham | Chris Walley | Kane O'Connell O'Flynn | Taylor Lee-Keating | Ciaran McCarthy | Lewis Brophy | Aaron Katambay | Alison Oliver | Charleigh Bailey | Ian Tabone | Rúaidhrí Conroy | Hilary Vesey | Keano Power | Tim Roche | Helen Behan | Garry McCarthy | Sophie McCarthy | Christine McSweeney | Jordan Kelly | Michael O'Donoghue | Aaron Hayes</t>
-  </si>
-  <si>
-    <t>Ireland | UK</t>
-  </si>
-  <si>
-    <t>BBC Film | Fís Éireann / Screen Ireland | Sleeper Films</t>
-  </si>
-  <si>
-    <t>tt31710990</t>
-  </si>
-  <si>
-    <t>Dreams</t>
-  </si>
-  <si>
-    <t>Michel Franco</t>
-  </si>
-  <si>
-    <t>Isaac Hernández | Eduardo Gonzalez | Hugo Costa Ramos | Julio Bernal | René Martínez | Nadia Chiney | Jessica Chastain | Rupert Friend | Marshall Bell | Nadia Flamenco | Ali Kiley | Areyla Faeron | Rafael Jiménez | Mercedes Hernández | Eligio Meléndez | Ana Echeverría | Azarel Govea | Brenda Alardín | Bryant Pineda | Camila Medellín | Carla Benassini | Germán Martínez | Helena Alonso | Jimena Esqueda Hernández | Karen Breidsprecher Wong | Leonardo Puchet | Mariana Arroyo Tinoco | Sinuhé Villalón | Martha Elena Trejo O'reilly | Magali Hernández</t>
-  </si>
-  <si>
-    <t>Drama | Romance | Thriller</t>
-  </si>
-  <si>
-    <t>USA | Mexico</t>
-  </si>
-  <si>
-    <t>English | Spanish</t>
-  </si>
-  <si>
-    <t>Teorema | Freckle Films | AR Content</t>
-  </si>
-  <si>
-    <t>tt14142060</t>
-  </si>
-  <si>
-    <t>Rental Family</t>
-  </si>
-  <si>
-    <t>Hikari</t>
-  </si>
-  <si>
-    <t>Brendan Fraser | Paolo Andrea Di Pietro | Shinji Ozeki | Takao Kin | Risa Kameda | Yuma Sonan | Kana Kitty | Gan Furukawa | Yuji Komatsu | Ryôko Osada | Helen Sadler | Kaoru Mizuki | Takehiro Hira | Mari Yamamoto | Shôhei Uno | Sonoe Mizoguchi | Keiji Yamashita | Kimura Bun | Yuki Kimura | Tsutomu Osabe | Rei Yukinaga | Shiho Asami | Seiga | Kazue Oda | Misato Morita | Daikichi Sugawara | Hideko Hara | Nanami Kawakami | Tamae Andô | Kan Kobayashi</t>
-  </si>
-  <si>
-    <t>Japan | USA</t>
-  </si>
-  <si>
-    <t>English | Japanese</t>
-  </si>
-  <si>
-    <t>Knockonwood | Domo Arigato Productions | Sight Unseen Pictures</t>
+    <t>France | Morocco | Belgium | UK</t>
+  </si>
+  <si>
+    <t>French | Arabic | English</t>
+  </si>
+  <si>
+    <t>Tessalit Productions | Furyo Films | Agora Films</t>
+  </si>
+  <si>
+    <t>tt32639175</t>
+  </si>
+  <si>
+    <t>Dolly</t>
+  </si>
+  <si>
+    <t>Rod Blackhurst</t>
+  </si>
+  <si>
+    <t>Fabianne Therese | Russ Tiller | Michalina Scorzelli | Kate Cobb | Ethan Suplee | Seann William Scott | Max the Impaler | Eve Blackhurst</t>
+  </si>
+  <si>
+    <t>Horror</t>
+  </si>
+  <si>
+    <t>Gentile Entertainment Group | Mama Bear Productions | Mama Bear Studios</t>
+  </si>
+  <si>
+    <t>tt35439895</t>
+  </si>
+  <si>
+    <t>Holding Liat</t>
+  </si>
+  <si>
+    <t>Brandon Kramer</t>
+  </si>
+  <si>
+    <t>Aviv Atzili | Aya Atzili | Liat Beinin Atzili | Netta Atzili | Ofri Atzili | Chaya Beinin | Joel Beinin | Tal Beinin | Yehuda Beinin</t>
+  </si>
+  <si>
+    <t>Documentary | Drama</t>
+  </si>
+  <si>
+    <t>English | Hebrew</t>
+  </si>
+  <si>
+    <t>Meridian Hill Pictures | Common Pictures | Kartemquin Films</t>
   </si>
 </sst>
 </file>
@@ -683,6 +775,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1027,11 +1120,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.578125" customWidth="1"/>
-    <col min="4" max="4" width="25.89453125" customWidth="1"/>
+    <col min="1" max="1" width="12.05078125" customWidth="1"/>
+    <col min="4" max="4" width="15.7890625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -1107,36 +1200,36 @@
         <v>20</v>
       </c>
       <c r="J2">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="K2" t="s">
         <v>21</v>
       </c>
       <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
       <c r="N2">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
-        <v>270</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
       </c>
       <c r="F3">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
@@ -1148,77 +1241,80 @@
         <v>28</v>
       </c>
       <c r="J3">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="O3">
-        <v>1178</v>
+        <v>7275</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>2026</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J4">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N4">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="O4">
-        <v>946</v>
+        <v>15114</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>41</v>
       </c>
       <c r="F5">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G5" t="s">
         <v>42</v>
@@ -1230,31 +1326,28 @@
         <v>44</v>
       </c>
       <c r="J5">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s">
         <v>45</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M5" t="s">
         <v>46</v>
       </c>
       <c r="N5">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="O5">
-        <v>1482</v>
+        <v>6781</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>47</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
       <c r="D6" t="s">
         <v>48</v>
       </c>
@@ -1271,159 +1364,162 @@
         <v>51</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N6">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N7">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="O7">
-        <v>54</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
       </c>
       <c r="J8">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N8">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="O8">
-        <v>13</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9">
         <v>2025</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="J9">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="K9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N9">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="O9">
-        <v>724</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="s">
         <v>81</v>
       </c>
       <c r="F10">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="G10" t="s">
         <v>82</v>
@@ -1435,25 +1531,22 @@
         <v>84</v>
       </c>
       <c r="J10">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="K10" t="s">
         <v>85</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="M10" t="s">
         <v>86</v>
       </c>
       <c r="N10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O10">
-        <v>9520</v>
-      </c>
-      <c r="P10">
-        <v>60000000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -1472,248 +1565,242 @@
       <c r="G11" t="s">
         <v>90</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>91</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11">
+        <v>86</v>
+      </c>
+      <c r="K11" t="s">
         <v>92</v>
       </c>
-      <c r="J11">
-        <v>111</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>93</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>94</v>
       </c>
-      <c r="M11" t="s">
-        <v>95</v>
-      </c>
       <c r="N11">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="O11">
-        <v>182</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
         <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>97</v>
       </c>
       <c r="F12">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G12" t="s">
         <v>98</v>
       </c>
+      <c r="H12" t="s">
+        <v>99</v>
+      </c>
       <c r="I12" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="J12">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="K12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" t="s">
         <v>100</v>
       </c>
-      <c r="L12" t="s">
-        <v>101</v>
-      </c>
-      <c r="M12" t="s">
-        <v>102</v>
-      </c>
       <c r="N12">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="O12">
-        <v>11</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" t="s">
         <v>103</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13">
+        <v>2026</v>
+      </c>
+      <c r="G13" t="s">
         <v>104</v>
       </c>
-      <c r="E13" t="s">
-        <v>104</v>
-      </c>
-      <c r="F13">
-        <v>2025</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>105</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13">
+        <v>101</v>
+      </c>
+      <c r="K13" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" t="s">
         <v>106</v>
       </c>
-      <c r="I13" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13">
-        <v>110</v>
-      </c>
-      <c r="K13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L13" t="s">
-        <v>109</v>
-      </c>
-      <c r="M13" t="s">
-        <v>110</v>
-      </c>
       <c r="N13">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="O13">
-        <v>10007</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14">
+        <v>2026</v>
+      </c>
+      <c r="G14" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" t="s">
         <v>111</v>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="I14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14">
+        <v>96</v>
+      </c>
+      <c r="K14" t="s">
         <v>112</v>
       </c>
-      <c r="E14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14">
-        <v>2025</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="L14" t="s">
         <v>113</v>
       </c>
-      <c r="H14" t="s">
+      <c r="M14" t="s">
         <v>114</v>
       </c>
-      <c r="I14" t="s">
-        <v>115</v>
-      </c>
-      <c r="J14">
-        <v>148</v>
-      </c>
-      <c r="K14" t="s">
-        <v>116</v>
-      </c>
-      <c r="L14" t="s">
-        <v>117</v>
-      </c>
-      <c r="M14" t="s">
-        <v>118</v>
-      </c>
       <c r="N14">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="O14">
-        <v>57125</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F15">
         <v>2025</v>
       </c>
       <c r="G15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15">
+        <v>119</v>
+      </c>
+      <c r="K15" t="s">
+        <v>120</v>
+      </c>
+      <c r="L15" t="s">
         <v>121</v>
       </c>
-      <c r="H15" t="s">
+      <c r="M15" t="s">
         <v>122</v>
       </c>
-      <c r="I15" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15">
-        <v>76</v>
-      </c>
-      <c r="K15" t="s">
-        <v>123</v>
-      </c>
-      <c r="L15" t="s">
-        <v>69</v>
-      </c>
-      <c r="M15" t="s">
-        <v>124</v>
-      </c>
       <c r="N15">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="O15">
-        <v>25</v>
+        <v>12857</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F16">
         <v>2025</v>
       </c>
       <c r="G16" t="s">
+        <v>125</v>
+      </c>
+      <c r="H16" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16">
+        <v>85</v>
+      </c>
+      <c r="K16" t="s">
         <v>127</v>
       </c>
-      <c r="H16" t="s">
+      <c r="L16" t="s">
         <v>128</v>
       </c>
-      <c r="I16" t="s">
+      <c r="M16" t="s">
         <v>129</v>
       </c>
-      <c r="J16">
-        <v>99</v>
-      </c>
-      <c r="K16" t="s">
-        <v>68</v>
-      </c>
-      <c r="L16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M16" t="s">
+      <c r="N16">
+        <v>7.2</v>
+      </c>
+      <c r="O16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
         <v>130</v>
       </c>
-      <c r="N16">
-        <v>6.2</v>
-      </c>
-      <c r="O16">
-        <v>180</v>
-      </c>
-      <c r="P16">
-        <v>30974400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
+      <c r="D17" t="s">
         <v>131</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>132</v>
       </c>
       <c r="E17" t="s">
         <v>132</v>
@@ -1731,25 +1818,25 @@
         <v>135</v>
       </c>
       <c r="J17">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="K17" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L17" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M17" t="s">
         <v>136</v>
       </c>
       <c r="N17">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="O17">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>137</v>
       </c>
@@ -1772,441 +1859,570 @@
         <v>142</v>
       </c>
       <c r="J18">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s">
         <v>143</v>
       </c>
       <c r="L18" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="M18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N18">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O18">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F19">
         <v>2025</v>
       </c>
       <c r="G19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="J19">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N19">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="O19">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>154</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F20">
         <v>2024</v>
       </c>
       <c r="G20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="J20">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="K20" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s">
-        <v>158</v>
+        <v>30</v>
       </c>
       <c r="M20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N20">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="O20">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>44579</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>162</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F21">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I21" t="s">
-        <v>60</v>
+        <v>166</v>
       </c>
       <c r="J21">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="K21" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L21" t="s">
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="M21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N21">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="O21">
-        <v>3095</v>
-      </c>
-      <c r="P21">
-        <v>22506151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>81827</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F22">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J22">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K22" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="L22" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="M22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N22">
+        <v>7.5</v>
+      </c>
+      <c r="O22">
+        <v>11072</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23">
+        <v>2026</v>
+      </c>
+      <c r="G23" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" t="s">
+        <v>180</v>
+      </c>
+      <c r="I23" t="s">
+        <v>181</v>
+      </c>
+      <c r="J23">
+        <v>98</v>
+      </c>
+      <c r="K23" t="s">
+        <v>182</v>
+      </c>
+      <c r="L23" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" t="s">
+        <v>183</v>
+      </c>
+      <c r="N23">
         <v>6.5</v>
       </c>
-      <c r="O22">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>173</v>
-      </c>
-      <c r="D23" t="s">
-        <v>174</v>
-      </c>
-      <c r="E23" t="s">
-        <v>174</v>
-      </c>
-      <c r="F23">
-        <v>2025</v>
-      </c>
-      <c r="G23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" t="s">
-        <v>176</v>
-      </c>
-      <c r="I23" t="s">
-        <v>99</v>
-      </c>
-      <c r="J23">
-        <v>80</v>
-      </c>
-      <c r="K23" t="s">
-        <v>52</v>
-      </c>
-      <c r="L23" t="s">
-        <v>53</v>
-      </c>
-      <c r="M23" t="s">
-        <v>177</v>
-      </c>
-      <c r="N23">
-        <v>7.1</v>
-      </c>
       <c r="O23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>20582</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
+        <v>184</v>
       </c>
       <c r="D24" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F24">
         <v>2026</v>
       </c>
       <c r="G24" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H24" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="I24" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="J24">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="K24" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="L24" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="M24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="O24">
-        <v>7252</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D25" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E25" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F25">
         <v>2025</v>
       </c>
       <c r="G25" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H25" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I25" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J25">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="K25" t="s">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="L25" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="M25" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N25">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="O25">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>34101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D26" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E26" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F26">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G26" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H26" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I26" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="J26">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="L26" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="M26" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N26">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="O26">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D27" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E27" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F27">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G27" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H27" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I27" t="s">
-        <v>204</v>
+        <v>28</v>
       </c>
       <c r="J27">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="K27" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N27">
-        <v>5.7</v>
+        <v>7.3</v>
       </c>
       <c r="O27">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E28" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F28">
         <v>2025</v>
       </c>
       <c r="G28" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H28" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I28" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="J28">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="K28" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="L28" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="M28" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="N28">
         <v>7.6</v>
       </c>
       <c r="O28">
-        <v>26912</v>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>221</v>
+      </c>
+      <c r="D29" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" t="s">
+        <v>222</v>
+      </c>
+      <c r="F29">
+        <v>2025</v>
+      </c>
+      <c r="G29" t="s">
+        <v>223</v>
+      </c>
+      <c r="H29" t="s">
+        <v>224</v>
+      </c>
+      <c r="I29" t="s">
+        <v>225</v>
+      </c>
+      <c r="J29">
+        <v>94</v>
+      </c>
+      <c r="K29" t="s">
+        <v>226</v>
+      </c>
+      <c r="L29" t="s">
+        <v>227</v>
+      </c>
+      <c r="M29" t="s">
+        <v>228</v>
+      </c>
+      <c r="N29">
+        <v>6.2</v>
+      </c>
+      <c r="O29">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>229</v>
+      </c>
+      <c r="D30" t="s">
+        <v>230</v>
+      </c>
+      <c r="E30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F30">
+        <v>2025</v>
+      </c>
+      <c r="G30" t="s">
+        <v>231</v>
+      </c>
+      <c r="H30" t="s">
+        <v>232</v>
+      </c>
+      <c r="I30" t="s">
+        <v>233</v>
+      </c>
+      <c r="J30">
+        <v>83</v>
+      </c>
+      <c r="K30" t="s">
+        <v>174</v>
+      </c>
+      <c r="L30" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" t="s">
+        <v>234</v>
+      </c>
+      <c r="N30">
+        <v>5.2</v>
+      </c>
+      <c r="O30">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>235</v>
+      </c>
+      <c r="D31" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" t="s">
+        <v>236</v>
+      </c>
+      <c r="F31">
+        <v>2025</v>
+      </c>
+      <c r="G31" t="s">
+        <v>237</v>
+      </c>
+      <c r="H31" t="s">
+        <v>238</v>
+      </c>
+      <c r="I31" t="s">
+        <v>239</v>
+      </c>
+      <c r="J31">
+        <v>97</v>
+      </c>
+      <c r="K31" t="s">
+        <v>174</v>
+      </c>
+      <c r="L31" t="s">
+        <v>240</v>
+      </c>
+      <c r="M31" t="s">
+        <v>241</v>
+      </c>
+      <c r="N31">
+        <v>6.9</v>
+      </c>
+      <c r="O31">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
